--- a/outlook-template-tool/Outlook邮件模板工具.xlsx
+++ b/outlook-template-tool/Outlook邮件模板工具.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="邮件工具" sheetId="1" r:id="R86fcf9adb3474243"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板库" sheetId="2" r:id="R8c6dfd2966fe4b15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设置说明" sheetId="3" r:id="R749ad97af41c4b3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="邮件工具" sheetId="1" r:id="R24d92273f8e44b28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板库" sheetId="2" r:id="Ra902dc05debe47ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="定时任务" sheetId="3" r:id="R9dbe57624d344dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设置说明" sheetId="4" r:id="R939688b9e98e463c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  <x:numFmts count="3">
+    <x:numFmt numFmtId="200" formatCode="hh:mm:ss"/>
+    <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd hh:mm:ss"/>
+    <x:numFmt numFmtId="202" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -93,17 +96,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE7E6E6"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFEEF5FB"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E6E6"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -176,6 +179,22 @@
       <x:left style="thin">
         <x:color rgb="FFB4C7E7"/>
       </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFB4C7E7"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFB4C7E7"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFB4C7E7"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB4C7E7"/>
+      </x:left>
       <x:top style="thin">
         <x:color rgb="FFB4C7E7"/>
       </x:top>
@@ -190,22 +209,6 @@
       <x:top style="thin">
         <x:color rgb="FFB4C7E7"/>
       </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFB4C7E7"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFB4C7E7"/>
-      </x:left>
-      <x:bottom style="thin">
-        <x:color rgb="FFB4C7E7"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:right style="thin">
-        <x:color rgb="FFB4C7E7"/>
-      </x:right>
       <x:bottom style="thin">
         <x:color rgb="FFB4C7E7"/>
       </x:bottom>
@@ -334,7 +337,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="129">
+  <x:cellXfs count="139">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -394,148 +397,133 @@
     <x:xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -651,6 +639,60 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="4" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -660,6 +702,9 @@
         </x:ext>
       </x:extLst>
     </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
       <x:extLst>
@@ -668,7 +713,7 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -682,7 +727,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -709,24 +754,18 @@
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1045,11 +1084,11 @@
       <x:c r="D7" s="12" t="str">
         <x:v>收件人</x:v>
       </x:c>
-      <x:c r="E7" s="36"/>
-      <x:c r="F7" s="37"/>
-      <x:c r="G7" s="37"/>
-      <x:c r="H7" s="37"/>
-      <x:c r="I7" s="38"/>
+      <x:c r="E7" s="31"/>
+      <x:c r="F7" s="32"/>
+      <x:c r="G7" s="32"/>
+      <x:c r="H7" s="32"/>
+      <x:c r="I7" s="33"/>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
       <x:c r="A8" s="12" t="str">
@@ -1062,11 +1101,11 @@
       <x:c r="D8" s="12" t="str">
         <x:v>抄送</x:v>
       </x:c>
-      <x:c r="E8" s="36"/>
-      <x:c r="F8" s="37"/>
-      <x:c r="G8" s="37"/>
-      <x:c r="H8" s="37"/>
-      <x:c r="I8" s="38"/>
+      <x:c r="E8" s="31"/>
+      <x:c r="F8" s="32"/>
+      <x:c r="G8" s="32"/>
+      <x:c r="H8" s="32"/>
+      <x:c r="I8" s="33"/>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
       <x:c r="A9" s="2"/>
@@ -1075,13 +1114,13 @@
       <x:c r="D9" s="12" t="str">
         <x:v>主题</x:v>
       </x:c>
-      <x:c r="E9" s="36"/>
-      <x:c r="F9" s="37"/>
-      <x:c r="G9" s="37"/>
-      <x:c r="H9" s="37"/>
-      <x:c r="I9" s="38"/>
-    </x:row>
-    <x:row r="10" ht="21" customHeight="1">
+      <x:c r="E9" s="31"/>
+      <x:c r="F9" s="32"/>
+      <x:c r="G9" s="32"/>
+      <x:c r="H9" s="32"/>
+      <x:c r="I9" s="33"/>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="20" t="str">
         <x:v>变量名</x:v>
       </x:c>
@@ -1096,14 +1135,9 @@
       <x:c r="H10" s="2"/>
       <x:c r="I10" s="2"/>
     </x:row>
-    <x:row r="11" ht="21" customHeight="1">
-      <x:c r="A11" s="24" t="str">
-        <x:v>batch_date</x:v>
-      </x:c>
-      <x:c r="B11" s="25" t="n">
-        <x:f>TODAY()-1</x:f>
-        <x:v>46280</x:v>
-      </x:c>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="21"/>
+      <x:c r="B11" s="25"/>
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="12" t="str">
         <x:v>正文</x:v>
@@ -1114,214 +1148,216 @@
       <x:c r="H11" s="12"/>
       <x:c r="I11" s="12"/>
     </x:row>
-    <x:row r="12" ht="21" customHeight="1">
-      <x:c r="A12" s="26"/>
-      <x:c r="B12" s="30"/>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="23"/>
+      <x:c r="B12" s="26"/>
       <x:c r="C12" s="2"/>
-      <x:c r="D12" s="56"/>
-      <x:c r="E12" s="57"/>
-      <x:c r="F12" s="57"/>
-      <x:c r="G12" s="57"/>
-      <x:c r="H12" s="57"/>
-      <x:c r="I12" s="58"/>
-    </x:row>
-    <x:row r="13" ht="21" customHeight="1">
-      <x:c r="A13" s="28"/>
-      <x:c r="B13" s="31"/>
+      <x:c r="D12" s="51"/>
+      <x:c r="E12" s="52"/>
+      <x:c r="F12" s="52"/>
+      <x:c r="G12" s="52"/>
+      <x:c r="H12" s="52"/>
+      <x:c r="I12" s="53"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="23"/>
+      <x:c r="B13" s="26"/>
       <x:c r="C13" s="2"/>
-      <x:c r="D13" s="59"/>
-      <x:c r="E13" s="60"/>
-      <x:c r="F13" s="60"/>
-      <x:c r="G13" s="60"/>
-      <x:c r="H13" s="60"/>
-      <x:c r="I13" s="61"/>
-    </x:row>
-    <x:row r="14" ht="21" customHeight="1">
-      <x:c r="A14" s="28"/>
-      <x:c r="B14" s="31"/>
+      <x:c r="D13" s="54"/>
+      <x:c r="E13" s="55"/>
+      <x:c r="F13" s="55"/>
+      <x:c r="G13" s="55"/>
+      <x:c r="H13" s="55"/>
+      <x:c r="I13" s="56"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="23"/>
+      <x:c r="B14" s="26"/>
       <x:c r="C14" s="2"/>
-      <x:c r="D14" s="59"/>
-      <x:c r="E14" s="60"/>
-      <x:c r="F14" s="60"/>
-      <x:c r="G14" s="60"/>
-      <x:c r="H14" s="60"/>
-      <x:c r="I14" s="61"/>
-    </x:row>
-    <x:row r="15" ht="21" customHeight="1">
-      <x:c r="A15" s="28"/>
-      <x:c r="B15" s="31"/>
+      <x:c r="D14" s="54"/>
+      <x:c r="E14" s="55"/>
+      <x:c r="F14" s="55"/>
+      <x:c r="G14" s="55"/>
+      <x:c r="H14" s="55"/>
+      <x:c r="I14" s="56"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="23"/>
+      <x:c r="B15" s="26"/>
       <x:c r="C15" s="2"/>
-      <x:c r="D15" s="59"/>
-      <x:c r="E15" s="60"/>
-      <x:c r="F15" s="60"/>
-      <x:c r="G15" s="60"/>
-      <x:c r="H15" s="60"/>
-      <x:c r="I15" s="61"/>
-    </x:row>
-    <x:row r="16" ht="21" customHeight="1">
-      <x:c r="A16" s="28"/>
-      <x:c r="B16" s="31"/>
+      <x:c r="D15" s="54"/>
+      <x:c r="E15" s="55"/>
+      <x:c r="F15" s="55"/>
+      <x:c r="G15" s="55"/>
+      <x:c r="H15" s="55"/>
+      <x:c r="I15" s="56"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="23"/>
+      <x:c r="B16" s="26"/>
       <x:c r="C16" s="2"/>
-      <x:c r="D16" s="59"/>
-      <x:c r="E16" s="60"/>
-      <x:c r="F16" s="60"/>
-      <x:c r="G16" s="60"/>
-      <x:c r="H16" s="60"/>
-      <x:c r="I16" s="61"/>
-    </x:row>
-    <x:row r="17" ht="21" customHeight="1">
-      <x:c r="A17" s="28"/>
-      <x:c r="B17" s="31"/>
+      <x:c r="D16" s="54"/>
+      <x:c r="E16" s="55"/>
+      <x:c r="F16" s="55"/>
+      <x:c r="G16" s="55"/>
+      <x:c r="H16" s="55"/>
+      <x:c r="I16" s="56"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
       <x:c r="C17" s="2"/>
-      <x:c r="D17" s="59"/>
-      <x:c r="E17" s="60"/>
-      <x:c r="F17" s="60"/>
-      <x:c r="G17" s="60"/>
-      <x:c r="H17" s="60"/>
-      <x:c r="I17" s="61"/>
-    </x:row>
-    <x:row r="18" ht="21" customHeight="1">
-      <x:c r="A18" s="28"/>
-      <x:c r="B18" s="31"/>
+      <x:c r="D17" s="54"/>
+      <x:c r="E17" s="55"/>
+      <x:c r="F17" s="55"/>
+      <x:c r="G17" s="55"/>
+      <x:c r="H17" s="55"/>
+      <x:c r="I17" s="56"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="16" t="str">
+        <x:v>导入宏后显示参数位置和滚动条</x:v>
+      </x:c>
+      <x:c r="B18" s="16"/>
       <x:c r="C18" s="2"/>
-      <x:c r="D18" s="59"/>
-      <x:c r="E18" s="60"/>
-      <x:c r="F18" s="60"/>
-      <x:c r="G18" s="60"/>
-      <x:c r="H18" s="60"/>
-      <x:c r="I18" s="61"/>
-    </x:row>
-    <x:row r="19" ht="21" customHeight="1">
-      <x:c r="A19" s="28"/>
-      <x:c r="B19" s="31"/>
+      <x:c r="D18" s="54"/>
+      <x:c r="E18" s="55"/>
+      <x:c r="F18" s="55"/>
+      <x:c r="G18" s="55"/>
+      <x:c r="H18" s="55"/>
+      <x:c r="I18" s="56"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2"/>
+      <x:c r="B19" s="2"/>
       <x:c r="C19" s="2"/>
-      <x:c r="D19" s="59"/>
-      <x:c r="E19" s="60"/>
-      <x:c r="F19" s="60"/>
-      <x:c r="G19" s="60"/>
-      <x:c r="H19" s="60"/>
-      <x:c r="I19" s="61"/>
-    </x:row>
-    <x:row r="20" ht="21" customHeight="1">
-      <x:c r="A20" s="28"/>
-      <x:c r="B20" s="31"/>
+      <x:c r="D19" s="54"/>
+      <x:c r="E19" s="55"/>
+      <x:c r="F19" s="55"/>
+      <x:c r="G19" s="55"/>
+      <x:c r="H19" s="55"/>
+      <x:c r="I19" s="56"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2"/>
+      <x:c r="B20" s="2"/>
       <x:c r="C20" s="2"/>
-      <x:c r="D20" s="59"/>
-      <x:c r="E20" s="60"/>
-      <x:c r="F20" s="60"/>
-      <x:c r="G20" s="60"/>
-      <x:c r="H20" s="60"/>
-      <x:c r="I20" s="61"/>
-    </x:row>
-    <x:row r="21" ht="21" customHeight="1">
-      <x:c r="A21" s="28"/>
-      <x:c r="B21" s="31"/>
+      <x:c r="D20" s="54"/>
+      <x:c r="E20" s="55"/>
+      <x:c r="F20" s="55"/>
+      <x:c r="G20" s="55"/>
+      <x:c r="H20" s="55"/>
+      <x:c r="I20" s="56"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2"/>
+      <x:c r="B21" s="2"/>
       <x:c r="C21" s="2"/>
-      <x:c r="D21" s="59"/>
-      <x:c r="E21" s="60"/>
-      <x:c r="F21" s="60"/>
-      <x:c r="G21" s="60"/>
-      <x:c r="H21" s="60"/>
-      <x:c r="I21" s="61"/>
-    </x:row>
-    <x:row r="22" ht="21" customHeight="1">
-      <x:c r="A22" s="28"/>
-      <x:c r="B22" s="31"/>
+      <x:c r="D21" s="54"/>
+      <x:c r="E21" s="55"/>
+      <x:c r="F21" s="55"/>
+      <x:c r="G21" s="55"/>
+      <x:c r="H21" s="55"/>
+      <x:c r="I21" s="56"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2"/>
+      <x:c r="B22" s="2"/>
       <x:c r="C22" s="2"/>
-      <x:c r="D22" s="59"/>
-      <x:c r="E22" s="60"/>
-      <x:c r="F22" s="60"/>
-      <x:c r="G22" s="60"/>
-      <x:c r="H22" s="60"/>
-      <x:c r="I22" s="61"/>
-    </x:row>
-    <x:row r="23" ht="21" customHeight="1">
-      <x:c r="A23" s="28"/>
-      <x:c r="B23" s="31"/>
+      <x:c r="D22" s="54"/>
+      <x:c r="E22" s="55"/>
+      <x:c r="F22" s="55"/>
+      <x:c r="G22" s="55"/>
+      <x:c r="H22" s="55"/>
+      <x:c r="I22" s="56"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2"/>
+      <x:c r="B23" s="2"/>
       <x:c r="C23" s="2"/>
-      <x:c r="D23" s="59"/>
-      <x:c r="E23" s="60"/>
-      <x:c r="F23" s="60"/>
-      <x:c r="G23" s="60"/>
-      <x:c r="H23" s="60"/>
-      <x:c r="I23" s="61"/>
-    </x:row>
-    <x:row r="24" ht="21" customHeight="1">
-      <x:c r="A24" s="28"/>
-      <x:c r="B24" s="31"/>
+      <x:c r="D23" s="54"/>
+      <x:c r="E23" s="55"/>
+      <x:c r="F23" s="55"/>
+      <x:c r="G23" s="55"/>
+      <x:c r="H23" s="55"/>
+      <x:c r="I23" s="56"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
       <x:c r="C24" s="2"/>
-      <x:c r="D24" s="59"/>
-      <x:c r="E24" s="60"/>
-      <x:c r="F24" s="60"/>
-      <x:c r="G24" s="60"/>
-      <x:c r="H24" s="60"/>
-      <x:c r="I24" s="61"/>
-    </x:row>
-    <x:row r="25" ht="21" customHeight="1">
-      <x:c r="A25" s="28"/>
-      <x:c r="B25" s="31"/>
+      <x:c r="D24" s="54"/>
+      <x:c r="E24" s="55"/>
+      <x:c r="F24" s="55"/>
+      <x:c r="G24" s="55"/>
+      <x:c r="H24" s="55"/>
+      <x:c r="I24" s="56"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="2"/>
       <x:c r="C25" s="2"/>
-      <x:c r="D25" s="59"/>
-      <x:c r="E25" s="60"/>
-      <x:c r="F25" s="60"/>
-      <x:c r="G25" s="60"/>
-      <x:c r="H25" s="60"/>
-      <x:c r="I25" s="61"/>
-    </x:row>
-    <x:row r="26" ht="21" customHeight="1">
-      <x:c r="A26" s="28"/>
-      <x:c r="B26" s="31"/>
+      <x:c r="D25" s="54"/>
+      <x:c r="E25" s="55"/>
+      <x:c r="F25" s="55"/>
+      <x:c r="G25" s="55"/>
+      <x:c r="H25" s="55"/>
+      <x:c r="I25" s="56"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2"/>
+      <x:c r="B26" s="2"/>
       <x:c r="C26" s="2"/>
-      <x:c r="D26" s="59"/>
-      <x:c r="E26" s="60"/>
-      <x:c r="F26" s="60"/>
-      <x:c r="G26" s="60"/>
-      <x:c r="H26" s="60"/>
-      <x:c r="I26" s="61"/>
-    </x:row>
-    <x:row r="27" ht="21" customHeight="1">
-      <x:c r="A27" s="28"/>
-      <x:c r="B27" s="31"/>
+      <x:c r="D26" s="54"/>
+      <x:c r="E26" s="55"/>
+      <x:c r="F26" s="55"/>
+      <x:c r="G26" s="55"/>
+      <x:c r="H26" s="55"/>
+      <x:c r="I26" s="56"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="2"/>
+      <x:c r="B27" s="2"/>
       <x:c r="C27" s="2"/>
-      <x:c r="D27" s="59"/>
-      <x:c r="E27" s="60"/>
-      <x:c r="F27" s="60"/>
-      <x:c r="G27" s="60"/>
-      <x:c r="H27" s="60"/>
-      <x:c r="I27" s="61"/>
-    </x:row>
-    <x:row r="28" ht="21" customHeight="1">
-      <x:c r="A28" s="28"/>
-      <x:c r="B28" s="31"/>
+      <x:c r="D27" s="54"/>
+      <x:c r="E27" s="55"/>
+      <x:c r="F27" s="55"/>
+      <x:c r="G27" s="55"/>
+      <x:c r="H27" s="55"/>
+      <x:c r="I27" s="56"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2"/>
+      <x:c r="B28" s="2"/>
       <x:c r="C28" s="2"/>
-      <x:c r="D28" s="59"/>
-      <x:c r="E28" s="60"/>
-      <x:c r="F28" s="60"/>
-      <x:c r="G28" s="60"/>
-      <x:c r="H28" s="60"/>
-      <x:c r="I28" s="61"/>
-    </x:row>
-    <x:row r="29" ht="21" customHeight="1">
-      <x:c r="A29" s="28"/>
-      <x:c r="B29" s="31"/>
+      <x:c r="D28" s="54"/>
+      <x:c r="E28" s="55"/>
+      <x:c r="F28" s="55"/>
+      <x:c r="G28" s="55"/>
+      <x:c r="H28" s="55"/>
+      <x:c r="I28" s="56"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
       <x:c r="C29" s="2"/>
-      <x:c r="D29" s="59"/>
-      <x:c r="E29" s="60"/>
-      <x:c r="F29" s="60"/>
-      <x:c r="G29" s="60"/>
-      <x:c r="H29" s="60"/>
-      <x:c r="I29" s="61"/>
-    </x:row>
-    <x:row r="30" ht="21" customHeight="1">
-      <x:c r="A30" s="28"/>
-      <x:c r="B30" s="31"/>
+      <x:c r="D29" s="54"/>
+      <x:c r="E29" s="55"/>
+      <x:c r="F29" s="55"/>
+      <x:c r="G29" s="55"/>
+      <x:c r="H29" s="55"/>
+      <x:c r="I29" s="56"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2"/>
+      <x:c r="B30" s="2"/>
       <x:c r="C30" s="2"/>
-      <x:c r="D30" s="62"/>
-      <x:c r="E30" s="63"/>
-      <x:c r="F30" s="63"/>
-      <x:c r="G30" s="63"/>
-      <x:c r="H30" s="63"/>
-      <x:c r="I30" s="64"/>
+      <x:c r="D30" s="57"/>
+      <x:c r="E30" s="58"/>
+      <x:c r="F30" s="58"/>
+      <x:c r="G30" s="58"/>
+      <x:c r="H30" s="58"/>
+      <x:c r="I30" s="59"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="2"/>
@@ -1338,16 +1374,16 @@
       <x:c r="A32" s="12" t="str">
         <x:v>状态</x:v>
       </x:c>
-      <x:c r="B32" s="66" t="str">
+      <x:c r="B32" s="61" t="str">
         <x:v>导入 VBA 模块后运行 SetupWorkbook。</x:v>
       </x:c>
-      <x:c r="C32" s="67"/>
-      <x:c r="D32" s="67"/>
-      <x:c r="E32" s="67"/>
-      <x:c r="F32" s="67"/>
-      <x:c r="G32" s="67"/>
-      <x:c r="H32" s="67"/>
-      <x:c r="I32" s="68"/>
+      <x:c r="C32" s="62"/>
+      <x:c r="D32" s="62"/>
+      <x:c r="E32" s="62"/>
+      <x:c r="F32" s="62"/>
+      <x:c r="G32" s="62"/>
+      <x:c r="H32" s="62"/>
+      <x:c r="I32" s="63"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="2"/>
@@ -1361,28 +1397,28 @@
       <x:c r="I33" s="2"/>
     </x:row>
     <x:row r="34" ht="23" customHeight="1">
-      <x:c r="A34" s="70" t="str">
-        <x:v>黄色单元格用于填写。batch_date 自动等于运行当天减 1 天，默认格式 yyyy-mm-dd。自动发送启用时，仍会先显示确认框。</x:v>
-      </x:c>
-      <x:c r="B34" s="70"/>
-      <x:c r="C34" s="70"/>
-      <x:c r="D34" s="70"/>
-      <x:c r="E34" s="70"/>
-      <x:c r="F34" s="70"/>
-      <x:c r="G34" s="70"/>
-      <x:c r="H34" s="70"/>
-      <x:c r="I34" s="70"/>
+      <x:c r="A34" s="65" t="str">
+        <x:v>参数仅在当前模板实际使用时显示。黄色为手动输入，灰色为日期等自动计算参数；参数区每页显示 6 项。</x:v>
+      </x:c>
+      <x:c r="B34" s="65"/>
+      <x:c r="C34" s="65"/>
+      <x:c r="D34" s="65"/>
+      <x:c r="E34" s="65"/>
+      <x:c r="F34" s="65"/>
+      <x:c r="G34" s="65"/>
+      <x:c r="H34" s="65"/>
+      <x:c r="I34" s="65"/>
     </x:row>
     <x:row r="35" ht="23" customHeight="1">
-      <x:c r="A35" s="70"/>
-      <x:c r="B35" s="70"/>
-      <x:c r="C35" s="70"/>
-      <x:c r="D35" s="70"/>
-      <x:c r="E35" s="70"/>
-      <x:c r="F35" s="70"/>
-      <x:c r="G35" s="70"/>
-      <x:c r="H35" s="70"/>
-      <x:c r="I35" s="70"/>
+      <x:c r="A35" s="65"/>
+      <x:c r="B35" s="65"/>
+      <x:c r="C35" s="65"/>
+      <x:c r="D35" s="65"/>
+      <x:c r="E35" s="65"/>
+      <x:c r="F35" s="65"/>
+      <x:c r="G35" s="65"/>
+      <x:c r="H35" s="65"/>
+      <x:c r="I35" s="65"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="2"/>
@@ -1421,6 +1457,7 @@
   <x:mergeCells>
     <x:mergeCell ref="A5:B5"/>
     <x:mergeCell ref="D5:I5"/>
+    <x:mergeCell ref="A18:B18"/>
     <x:mergeCell ref="E7:I7"/>
     <x:mergeCell ref="E8:I8"/>
     <x:mergeCell ref="E9:I9"/>
@@ -1477,7 +1514,7 @@
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
     </x:row>
-    <x:row r="4" ht="36" customHeight="1">
+    <x:row r="4" ht="40" customHeight="1">
       <x:c r="A4" s="20" t="str">
         <x:v>模板名称</x:v>
       </x:c>
@@ -1494,727 +1531,727 @@
         <x:v>正文</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="36" customHeight="1">
-      <x:c r="A5" s="98" t="str">
+    <x:row r="5" ht="40" customHeight="1">
+      <x:c r="A5" s="93" t="str">
         <x:v>付款提醒</x:v>
       </x:c>
-      <x:c r="B5" s="99" t="str">
+      <x:c r="B5" s="94" t="str">
         <x:v>{{收件人姓名}}&lt;{{收件人邮箱}}&gt;</x:v>
       </x:c>
-      <x:c r="C5" s="99" t="str"/>
-      <x:c r="D5" s="99" t="str">
+      <x:c r="C5" s="94" t="str"/>
+      <x:c r="D5" s="94" t="str">
         <x:v>付款提醒 - {{姓名}} - {{batch_date}}</x:v>
       </x:c>
-      <x:c r="E5" s="100" t="str">
+      <x:c r="E5" s="95" t="str">
         <x:v>您好，{{姓名}}：
 请确认截至 {{batch_date}} 的款项，金额为 {{金额}}。
 谢谢。</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="101" t="str">
+    <x:row r="6" ht="40" customHeight="1">
+      <x:c r="A6" s="96" t="str">
         <x:v>付款提醒（含抄送）</x:v>
       </x:c>
-      <x:c r="B6" s="102" t="str">
+      <x:c r="B6" s="97" t="str">
         <x:v>{{收件人姓名}}&lt;{{收件人邮箱}}&gt;</x:v>
       </x:c>
-      <x:c r="C6" s="102" t="str">
+      <x:c r="C6" s="97" t="str">
         <x:v>{{抄送人姓名}}&lt;{{抄送人邮箱}}&gt;</x:v>
       </x:c>
-      <x:c r="D6" s="102" t="str">
+      <x:c r="D6" s="97" t="str">
         <x:v>付款提醒 - {{姓名}} - {{batch_date}}</x:v>
       </x:c>
-      <x:c r="E6" s="103" t="str">
+      <x:c r="E6" s="98" t="str">
         <x:v>您好，{{姓名}}：
 请确认截至 {{batch_date}} 的款项，金额为 {{金额}}。
 谢谢。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="101"/>
-      <x:c r="B7" s="102"/>
-      <x:c r="C7" s="102"/>
-      <x:c r="D7" s="102"/>
-      <x:c r="E7" s="103"/>
+      <x:c r="A7" s="96"/>
+      <x:c r="B7" s="97"/>
+      <x:c r="C7" s="97"/>
+      <x:c r="D7" s="97"/>
+      <x:c r="E7" s="98"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="101"/>
-      <x:c r="B8" s="102"/>
-      <x:c r="C8" s="102"/>
-      <x:c r="D8" s="102"/>
-      <x:c r="E8" s="103"/>
+      <x:c r="A8" s="96"/>
+      <x:c r="B8" s="97"/>
+      <x:c r="C8" s="97"/>
+      <x:c r="D8" s="97"/>
+      <x:c r="E8" s="98"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="101"/>
-      <x:c r="B9" s="102"/>
-      <x:c r="C9" s="102"/>
-      <x:c r="D9" s="102"/>
-      <x:c r="E9" s="103"/>
+      <x:c r="A9" s="96"/>
+      <x:c r="B9" s="97"/>
+      <x:c r="C9" s="97"/>
+      <x:c r="D9" s="97"/>
+      <x:c r="E9" s="98"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="101"/>
-      <x:c r="B10" s="102"/>
-      <x:c r="C10" s="102"/>
-      <x:c r="D10" s="102"/>
-      <x:c r="E10" s="103"/>
+      <x:c r="A10" s="96"/>
+      <x:c r="B10" s="97"/>
+      <x:c r="C10" s="97"/>
+      <x:c r="D10" s="97"/>
+      <x:c r="E10" s="98"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="101"/>
-      <x:c r="B11" s="102"/>
-      <x:c r="C11" s="102"/>
-      <x:c r="D11" s="102"/>
-      <x:c r="E11" s="103"/>
+      <x:c r="A11" s="96"/>
+      <x:c r="B11" s="97"/>
+      <x:c r="C11" s="97"/>
+      <x:c r="D11" s="97"/>
+      <x:c r="E11" s="98"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="101"/>
-      <x:c r="B12" s="102"/>
-      <x:c r="C12" s="102"/>
-      <x:c r="D12" s="102"/>
-      <x:c r="E12" s="103"/>
+      <x:c r="A12" s="96"/>
+      <x:c r="B12" s="97"/>
+      <x:c r="C12" s="97"/>
+      <x:c r="D12" s="97"/>
+      <x:c r="E12" s="98"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="101"/>
-      <x:c r="B13" s="102"/>
-      <x:c r="C13" s="102"/>
-      <x:c r="D13" s="102"/>
-      <x:c r="E13" s="103"/>
+      <x:c r="A13" s="96"/>
+      <x:c r="B13" s="97"/>
+      <x:c r="C13" s="97"/>
+      <x:c r="D13" s="97"/>
+      <x:c r="E13" s="98"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="101"/>
-      <x:c r="B14" s="102"/>
-      <x:c r="C14" s="102"/>
-      <x:c r="D14" s="102"/>
-      <x:c r="E14" s="103"/>
+      <x:c r="A14" s="96"/>
+      <x:c r="B14" s="97"/>
+      <x:c r="C14" s="97"/>
+      <x:c r="D14" s="97"/>
+      <x:c r="E14" s="98"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="101"/>
-      <x:c r="B15" s="102"/>
-      <x:c r="C15" s="102"/>
-      <x:c r="D15" s="102"/>
-      <x:c r="E15" s="103"/>
+      <x:c r="A15" s="96"/>
+      <x:c r="B15" s="97"/>
+      <x:c r="C15" s="97"/>
+      <x:c r="D15" s="97"/>
+      <x:c r="E15" s="98"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="101"/>
-      <x:c r="B16" s="102"/>
-      <x:c r="C16" s="102"/>
-      <x:c r="D16" s="102"/>
-      <x:c r="E16" s="103"/>
+      <x:c r="A16" s="96"/>
+      <x:c r="B16" s="97"/>
+      <x:c r="C16" s="97"/>
+      <x:c r="D16" s="97"/>
+      <x:c r="E16" s="98"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="101"/>
-      <x:c r="B17" s="102"/>
-      <x:c r="C17" s="102"/>
-      <x:c r="D17" s="102"/>
-      <x:c r="E17" s="103"/>
+      <x:c r="A17" s="96"/>
+      <x:c r="B17" s="97"/>
+      <x:c r="C17" s="97"/>
+      <x:c r="D17" s="97"/>
+      <x:c r="E17" s="98"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="101"/>
-      <x:c r="B18" s="102"/>
-      <x:c r="C18" s="102"/>
-      <x:c r="D18" s="102"/>
-      <x:c r="E18" s="103"/>
+      <x:c r="A18" s="96"/>
+      <x:c r="B18" s="97"/>
+      <x:c r="C18" s="97"/>
+      <x:c r="D18" s="97"/>
+      <x:c r="E18" s="98"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="101"/>
-      <x:c r="B19" s="102"/>
-      <x:c r="C19" s="102"/>
-      <x:c r="D19" s="102"/>
-      <x:c r="E19" s="103"/>
+      <x:c r="A19" s="96"/>
+      <x:c r="B19" s="97"/>
+      <x:c r="C19" s="97"/>
+      <x:c r="D19" s="97"/>
+      <x:c r="E19" s="98"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="101"/>
-      <x:c r="B20" s="102"/>
-      <x:c r="C20" s="102"/>
-      <x:c r="D20" s="102"/>
-      <x:c r="E20" s="103"/>
+      <x:c r="A20" s="96"/>
+      <x:c r="B20" s="97"/>
+      <x:c r="C20" s="97"/>
+      <x:c r="D20" s="97"/>
+      <x:c r="E20" s="98"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="101"/>
-      <x:c r="B21" s="102"/>
-      <x:c r="C21" s="102"/>
-      <x:c r="D21" s="102"/>
-      <x:c r="E21" s="103"/>
+      <x:c r="A21" s="96"/>
+      <x:c r="B21" s="97"/>
+      <x:c r="C21" s="97"/>
+      <x:c r="D21" s="97"/>
+      <x:c r="E21" s="98"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="101"/>
-      <x:c r="B22" s="102"/>
-      <x:c r="C22" s="102"/>
-      <x:c r="D22" s="102"/>
-      <x:c r="E22" s="103"/>
+      <x:c r="A22" s="96"/>
+      <x:c r="B22" s="97"/>
+      <x:c r="C22" s="97"/>
+      <x:c r="D22" s="97"/>
+      <x:c r="E22" s="98"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="101"/>
-      <x:c r="B23" s="102"/>
-      <x:c r="C23" s="102"/>
-      <x:c r="D23" s="102"/>
-      <x:c r="E23" s="103"/>
+      <x:c r="A23" s="96"/>
+      <x:c r="B23" s="97"/>
+      <x:c r="C23" s="97"/>
+      <x:c r="D23" s="97"/>
+      <x:c r="E23" s="98"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="101"/>
-      <x:c r="B24" s="102"/>
-      <x:c r="C24" s="102"/>
-      <x:c r="D24" s="102"/>
-      <x:c r="E24" s="103"/>
+      <x:c r="A24" s="96"/>
+      <x:c r="B24" s="97"/>
+      <x:c r="C24" s="97"/>
+      <x:c r="D24" s="97"/>
+      <x:c r="E24" s="98"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="101"/>
-      <x:c r="B25" s="102"/>
-      <x:c r="C25" s="102"/>
-      <x:c r="D25" s="102"/>
-      <x:c r="E25" s="103"/>
+      <x:c r="A25" s="96"/>
+      <x:c r="B25" s="97"/>
+      <x:c r="C25" s="97"/>
+      <x:c r="D25" s="97"/>
+      <x:c r="E25" s="98"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="101"/>
-      <x:c r="B26" s="102"/>
-      <x:c r="C26" s="102"/>
-      <x:c r="D26" s="102"/>
-      <x:c r="E26" s="103"/>
+      <x:c r="A26" s="96"/>
+      <x:c r="B26" s="97"/>
+      <x:c r="C26" s="97"/>
+      <x:c r="D26" s="97"/>
+      <x:c r="E26" s="98"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="101"/>
-      <x:c r="B27" s="102"/>
-      <x:c r="C27" s="102"/>
-      <x:c r="D27" s="102"/>
-      <x:c r="E27" s="103"/>
+      <x:c r="A27" s="96"/>
+      <x:c r="B27" s="97"/>
+      <x:c r="C27" s="97"/>
+      <x:c r="D27" s="97"/>
+      <x:c r="E27" s="98"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="101"/>
-      <x:c r="B28" s="102"/>
-      <x:c r="C28" s="102"/>
-      <x:c r="D28" s="102"/>
-      <x:c r="E28" s="103"/>
+      <x:c r="A28" s="96"/>
+      <x:c r="B28" s="97"/>
+      <x:c r="C28" s="97"/>
+      <x:c r="D28" s="97"/>
+      <x:c r="E28" s="98"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="101"/>
-      <x:c r="B29" s="102"/>
-      <x:c r="C29" s="102"/>
-      <x:c r="D29" s="102"/>
-      <x:c r="E29" s="103"/>
+      <x:c r="A29" s="96"/>
+      <x:c r="B29" s="97"/>
+      <x:c r="C29" s="97"/>
+      <x:c r="D29" s="97"/>
+      <x:c r="E29" s="98"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="101"/>
-      <x:c r="B30" s="102"/>
-      <x:c r="C30" s="102"/>
-      <x:c r="D30" s="102"/>
-      <x:c r="E30" s="103"/>
+      <x:c r="A30" s="96"/>
+      <x:c r="B30" s="97"/>
+      <x:c r="C30" s="97"/>
+      <x:c r="D30" s="97"/>
+      <x:c r="E30" s="98"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="101"/>
-      <x:c r="B31" s="102"/>
-      <x:c r="C31" s="102"/>
-      <x:c r="D31" s="102"/>
-      <x:c r="E31" s="103"/>
+      <x:c r="A31" s="96"/>
+      <x:c r="B31" s="97"/>
+      <x:c r="C31" s="97"/>
+      <x:c r="D31" s="97"/>
+      <x:c r="E31" s="98"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="101"/>
-      <x:c r="B32" s="102"/>
-      <x:c r="C32" s="102"/>
-      <x:c r="D32" s="102"/>
-      <x:c r="E32" s="103"/>
+      <x:c r="A32" s="96"/>
+      <x:c r="B32" s="97"/>
+      <x:c r="C32" s="97"/>
+      <x:c r="D32" s="97"/>
+      <x:c r="E32" s="98"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="101"/>
-      <x:c r="B33" s="102"/>
-      <x:c r="C33" s="102"/>
-      <x:c r="D33" s="102"/>
-      <x:c r="E33" s="103"/>
+      <x:c r="A33" s="96"/>
+      <x:c r="B33" s="97"/>
+      <x:c r="C33" s="97"/>
+      <x:c r="D33" s="97"/>
+      <x:c r="E33" s="98"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="101"/>
-      <x:c r="B34" s="102"/>
-      <x:c r="C34" s="102"/>
-      <x:c r="D34" s="102"/>
-      <x:c r="E34" s="103"/>
+      <x:c r="A34" s="96"/>
+      <x:c r="B34" s="97"/>
+      <x:c r="C34" s="97"/>
+      <x:c r="D34" s="97"/>
+      <x:c r="E34" s="98"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="101"/>
-      <x:c r="B35" s="102"/>
-      <x:c r="C35" s="102"/>
-      <x:c r="D35" s="102"/>
-      <x:c r="E35" s="103"/>
+      <x:c r="A35" s="96"/>
+      <x:c r="B35" s="97"/>
+      <x:c r="C35" s="97"/>
+      <x:c r="D35" s="97"/>
+      <x:c r="E35" s="98"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="101"/>
-      <x:c r="B36" s="102"/>
-      <x:c r="C36" s="102"/>
-      <x:c r="D36" s="102"/>
-      <x:c r="E36" s="103"/>
+      <x:c r="A36" s="96"/>
+      <x:c r="B36" s="97"/>
+      <x:c r="C36" s="97"/>
+      <x:c r="D36" s="97"/>
+      <x:c r="E36" s="98"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="101"/>
-      <x:c r="B37" s="102"/>
-      <x:c r="C37" s="102"/>
-      <x:c r="D37" s="102"/>
-      <x:c r="E37" s="103"/>
+      <x:c r="A37" s="96"/>
+      <x:c r="B37" s="97"/>
+      <x:c r="C37" s="97"/>
+      <x:c r="D37" s="97"/>
+      <x:c r="E37" s="98"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="101"/>
-      <x:c r="B38" s="102"/>
-      <x:c r="C38" s="102"/>
-      <x:c r="D38" s="102"/>
-      <x:c r="E38" s="103"/>
+      <x:c r="A38" s="96"/>
+      <x:c r="B38" s="97"/>
+      <x:c r="C38" s="97"/>
+      <x:c r="D38" s="97"/>
+      <x:c r="E38" s="98"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="101"/>
-      <x:c r="B39" s="102"/>
-      <x:c r="C39" s="102"/>
-      <x:c r="D39" s="102"/>
-      <x:c r="E39" s="103"/>
+      <x:c r="A39" s="96"/>
+      <x:c r="B39" s="97"/>
+      <x:c r="C39" s="97"/>
+      <x:c r="D39" s="97"/>
+      <x:c r="E39" s="98"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="101"/>
-      <x:c r="B40" s="102"/>
-      <x:c r="C40" s="102"/>
-      <x:c r="D40" s="102"/>
-      <x:c r="E40" s="103"/>
+      <x:c r="A40" s="96"/>
+      <x:c r="B40" s="97"/>
+      <x:c r="C40" s="97"/>
+      <x:c r="D40" s="97"/>
+      <x:c r="E40" s="98"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="101"/>
-      <x:c r="B41" s="102"/>
-      <x:c r="C41" s="102"/>
-      <x:c r="D41" s="102"/>
-      <x:c r="E41" s="103"/>
+      <x:c r="A41" s="96"/>
+      <x:c r="B41" s="97"/>
+      <x:c r="C41" s="97"/>
+      <x:c r="D41" s="97"/>
+      <x:c r="E41" s="98"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="101"/>
-      <x:c r="B42" s="102"/>
-      <x:c r="C42" s="102"/>
-      <x:c r="D42" s="102"/>
-      <x:c r="E42" s="103"/>
+      <x:c r="A42" s="96"/>
+      <x:c r="B42" s="97"/>
+      <x:c r="C42" s="97"/>
+      <x:c r="D42" s="97"/>
+      <x:c r="E42" s="98"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="101"/>
-      <x:c r="B43" s="102"/>
-      <x:c r="C43" s="102"/>
-      <x:c r="D43" s="102"/>
-      <x:c r="E43" s="103"/>
+      <x:c r="A43" s="96"/>
+      <x:c r="B43" s="97"/>
+      <x:c r="C43" s="97"/>
+      <x:c r="D43" s="97"/>
+      <x:c r="E43" s="98"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="101"/>
-      <x:c r="B44" s="102"/>
-      <x:c r="C44" s="102"/>
-      <x:c r="D44" s="102"/>
-      <x:c r="E44" s="103"/>
+      <x:c r="A44" s="96"/>
+      <x:c r="B44" s="97"/>
+      <x:c r="C44" s="97"/>
+      <x:c r="D44" s="97"/>
+      <x:c r="E44" s="98"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="101"/>
-      <x:c r="B45" s="102"/>
-      <x:c r="C45" s="102"/>
-      <x:c r="D45" s="102"/>
-      <x:c r="E45" s="103"/>
+      <x:c r="A45" s="96"/>
+      <x:c r="B45" s="97"/>
+      <x:c r="C45" s="97"/>
+      <x:c r="D45" s="97"/>
+      <x:c r="E45" s="98"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="101"/>
-      <x:c r="B46" s="102"/>
-      <x:c r="C46" s="102"/>
-      <x:c r="D46" s="102"/>
-      <x:c r="E46" s="103"/>
+      <x:c r="A46" s="96"/>
+      <x:c r="B46" s="97"/>
+      <x:c r="C46" s="97"/>
+      <x:c r="D46" s="97"/>
+      <x:c r="E46" s="98"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="101"/>
-      <x:c r="B47" s="102"/>
-      <x:c r="C47" s="102"/>
-      <x:c r="D47" s="102"/>
-      <x:c r="E47" s="103"/>
+      <x:c r="A47" s="96"/>
+      <x:c r="B47" s="97"/>
+      <x:c r="C47" s="97"/>
+      <x:c r="D47" s="97"/>
+      <x:c r="E47" s="98"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="101"/>
-      <x:c r="B48" s="102"/>
-      <x:c r="C48" s="102"/>
-      <x:c r="D48" s="102"/>
-      <x:c r="E48" s="103"/>
+      <x:c r="A48" s="96"/>
+      <x:c r="B48" s="97"/>
+      <x:c r="C48" s="97"/>
+      <x:c r="D48" s="97"/>
+      <x:c r="E48" s="98"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="101"/>
-      <x:c r="B49" s="102"/>
-      <x:c r="C49" s="102"/>
-      <x:c r="D49" s="102"/>
-      <x:c r="E49" s="103"/>
+      <x:c r="A49" s="96"/>
+      <x:c r="B49" s="97"/>
+      <x:c r="C49" s="97"/>
+      <x:c r="D49" s="97"/>
+      <x:c r="E49" s="98"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="101"/>
-      <x:c r="B50" s="102"/>
-      <x:c r="C50" s="102"/>
-      <x:c r="D50" s="102"/>
-      <x:c r="E50" s="103"/>
+      <x:c r="A50" s="96"/>
+      <x:c r="B50" s="97"/>
+      <x:c r="C50" s="97"/>
+      <x:c r="D50" s="97"/>
+      <x:c r="E50" s="98"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="101"/>
-      <x:c r="B51" s="102"/>
-      <x:c r="C51" s="102"/>
-      <x:c r="D51" s="102"/>
-      <x:c r="E51" s="103"/>
+      <x:c r="A51" s="96"/>
+      <x:c r="B51" s="97"/>
+      <x:c r="C51" s="97"/>
+      <x:c r="D51" s="97"/>
+      <x:c r="E51" s="98"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="101"/>
-      <x:c r="B52" s="102"/>
-      <x:c r="C52" s="102"/>
-      <x:c r="D52" s="102"/>
-      <x:c r="E52" s="103"/>
+      <x:c r="A52" s="96"/>
+      <x:c r="B52" s="97"/>
+      <x:c r="C52" s="97"/>
+      <x:c r="D52" s="97"/>
+      <x:c r="E52" s="98"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="101"/>
-      <x:c r="B53" s="102"/>
-      <x:c r="C53" s="102"/>
-      <x:c r="D53" s="102"/>
-      <x:c r="E53" s="103"/>
+      <x:c r="A53" s="96"/>
+      <x:c r="B53" s="97"/>
+      <x:c r="C53" s="97"/>
+      <x:c r="D53" s="97"/>
+      <x:c r="E53" s="98"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="101"/>
-      <x:c r="B54" s="102"/>
-      <x:c r="C54" s="102"/>
-      <x:c r="D54" s="102"/>
-      <x:c r="E54" s="103"/>
+      <x:c r="A54" s="96"/>
+      <x:c r="B54" s="97"/>
+      <x:c r="C54" s="97"/>
+      <x:c r="D54" s="97"/>
+      <x:c r="E54" s="98"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="101"/>
-      <x:c r="B55" s="102"/>
-      <x:c r="C55" s="102"/>
-      <x:c r="D55" s="102"/>
-      <x:c r="E55" s="103"/>
+      <x:c r="A55" s="96"/>
+      <x:c r="B55" s="97"/>
+      <x:c r="C55" s="97"/>
+      <x:c r="D55" s="97"/>
+      <x:c r="E55" s="98"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="101"/>
-      <x:c r="B56" s="102"/>
-      <x:c r="C56" s="102"/>
-      <x:c r="D56" s="102"/>
-      <x:c r="E56" s="103"/>
+      <x:c r="A56" s="96"/>
+      <x:c r="B56" s="97"/>
+      <x:c r="C56" s="97"/>
+      <x:c r="D56" s="97"/>
+      <x:c r="E56" s="98"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="101"/>
-      <x:c r="B57" s="102"/>
-      <x:c r="C57" s="102"/>
-      <x:c r="D57" s="102"/>
-      <x:c r="E57" s="103"/>
+      <x:c r="A57" s="96"/>
+      <x:c r="B57" s="97"/>
+      <x:c r="C57" s="97"/>
+      <x:c r="D57" s="97"/>
+      <x:c r="E57" s="98"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="101"/>
-      <x:c r="B58" s="102"/>
-      <x:c r="C58" s="102"/>
-      <x:c r="D58" s="102"/>
-      <x:c r="E58" s="103"/>
+      <x:c r="A58" s="96"/>
+      <x:c r="B58" s="97"/>
+      <x:c r="C58" s="97"/>
+      <x:c r="D58" s="97"/>
+      <x:c r="E58" s="98"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="101"/>
-      <x:c r="B59" s="102"/>
-      <x:c r="C59" s="102"/>
-      <x:c r="D59" s="102"/>
-      <x:c r="E59" s="103"/>
+      <x:c r="A59" s="96"/>
+      <x:c r="B59" s="97"/>
+      <x:c r="C59" s="97"/>
+      <x:c r="D59" s="97"/>
+      <x:c r="E59" s="98"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="101"/>
-      <x:c r="B60" s="102"/>
-      <x:c r="C60" s="102"/>
-      <x:c r="D60" s="102"/>
-      <x:c r="E60" s="103"/>
+      <x:c r="A60" s="96"/>
+      <x:c r="B60" s="97"/>
+      <x:c r="C60" s="97"/>
+      <x:c r="D60" s="97"/>
+      <x:c r="E60" s="98"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="101"/>
-      <x:c r="B61" s="102"/>
-      <x:c r="C61" s="102"/>
-      <x:c r="D61" s="102"/>
-      <x:c r="E61" s="103"/>
+      <x:c r="A61" s="96"/>
+      <x:c r="B61" s="97"/>
+      <x:c r="C61" s="97"/>
+      <x:c r="D61" s="97"/>
+      <x:c r="E61" s="98"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="101"/>
-      <x:c r="B62" s="102"/>
-      <x:c r="C62" s="102"/>
-      <x:c r="D62" s="102"/>
-      <x:c r="E62" s="103"/>
+      <x:c r="A62" s="96"/>
+      <x:c r="B62" s="97"/>
+      <x:c r="C62" s="97"/>
+      <x:c r="D62" s="97"/>
+      <x:c r="E62" s="98"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="101"/>
-      <x:c r="B63" s="102"/>
-      <x:c r="C63" s="102"/>
-      <x:c r="D63" s="102"/>
-      <x:c r="E63" s="103"/>
+      <x:c r="A63" s="96"/>
+      <x:c r="B63" s="97"/>
+      <x:c r="C63" s="97"/>
+      <x:c r="D63" s="97"/>
+      <x:c r="E63" s="98"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="101"/>
-      <x:c r="B64" s="102"/>
-      <x:c r="C64" s="102"/>
-      <x:c r="D64" s="102"/>
-      <x:c r="E64" s="103"/>
+      <x:c r="A64" s="96"/>
+      <x:c r="B64" s="97"/>
+      <x:c r="C64" s="97"/>
+      <x:c r="D64" s="97"/>
+      <x:c r="E64" s="98"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="101"/>
-      <x:c r="B65" s="102"/>
-      <x:c r="C65" s="102"/>
-      <x:c r="D65" s="102"/>
-      <x:c r="E65" s="103"/>
+      <x:c r="A65" s="96"/>
+      <x:c r="B65" s="97"/>
+      <x:c r="C65" s="97"/>
+      <x:c r="D65" s="97"/>
+      <x:c r="E65" s="98"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="101"/>
-      <x:c r="B66" s="102"/>
-      <x:c r="C66" s="102"/>
-      <x:c r="D66" s="102"/>
-      <x:c r="E66" s="103"/>
+      <x:c r="A66" s="96"/>
+      <x:c r="B66" s="97"/>
+      <x:c r="C66" s="97"/>
+      <x:c r="D66" s="97"/>
+      <x:c r="E66" s="98"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="101"/>
-      <x:c r="B67" s="102"/>
-      <x:c r="C67" s="102"/>
-      <x:c r="D67" s="102"/>
-      <x:c r="E67" s="103"/>
+      <x:c r="A67" s="96"/>
+      <x:c r="B67" s="97"/>
+      <x:c r="C67" s="97"/>
+      <x:c r="D67" s="97"/>
+      <x:c r="E67" s="98"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="101"/>
-      <x:c r="B68" s="102"/>
-      <x:c r="C68" s="102"/>
-      <x:c r="D68" s="102"/>
-      <x:c r="E68" s="103"/>
+      <x:c r="A68" s="96"/>
+      <x:c r="B68" s="97"/>
+      <x:c r="C68" s="97"/>
+      <x:c r="D68" s="97"/>
+      <x:c r="E68" s="98"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="101"/>
-      <x:c r="B69" s="102"/>
-      <x:c r="C69" s="102"/>
-      <x:c r="D69" s="102"/>
-      <x:c r="E69" s="103"/>
+      <x:c r="A69" s="96"/>
+      <x:c r="B69" s="97"/>
+      <x:c r="C69" s="97"/>
+      <x:c r="D69" s="97"/>
+      <x:c r="E69" s="98"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="101"/>
-      <x:c r="B70" s="102"/>
-      <x:c r="C70" s="102"/>
-      <x:c r="D70" s="102"/>
-      <x:c r="E70" s="103"/>
+      <x:c r="A70" s="96"/>
+      <x:c r="B70" s="97"/>
+      <x:c r="C70" s="97"/>
+      <x:c r="D70" s="97"/>
+      <x:c r="E70" s="98"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="101"/>
-      <x:c r="B71" s="102"/>
-      <x:c r="C71" s="102"/>
-      <x:c r="D71" s="102"/>
-      <x:c r="E71" s="103"/>
+      <x:c r="A71" s="96"/>
+      <x:c r="B71" s="97"/>
+      <x:c r="C71" s="97"/>
+      <x:c r="D71" s="97"/>
+      <x:c r="E71" s="98"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="101"/>
-      <x:c r="B72" s="102"/>
-      <x:c r="C72" s="102"/>
-      <x:c r="D72" s="102"/>
-      <x:c r="E72" s="103"/>
+      <x:c r="A72" s="96"/>
+      <x:c r="B72" s="97"/>
+      <x:c r="C72" s="97"/>
+      <x:c r="D72" s="97"/>
+      <x:c r="E72" s="98"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="101"/>
-      <x:c r="B73" s="102"/>
-      <x:c r="C73" s="102"/>
-      <x:c r="D73" s="102"/>
-      <x:c r="E73" s="103"/>
+      <x:c r="A73" s="96"/>
+      <x:c r="B73" s="97"/>
+      <x:c r="C73" s="97"/>
+      <x:c r="D73" s="97"/>
+      <x:c r="E73" s="98"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="101"/>
-      <x:c r="B74" s="102"/>
-      <x:c r="C74" s="102"/>
-      <x:c r="D74" s="102"/>
-      <x:c r="E74" s="103"/>
+      <x:c r="A74" s="96"/>
+      <x:c r="B74" s="97"/>
+      <x:c r="C74" s="97"/>
+      <x:c r="D74" s="97"/>
+      <x:c r="E74" s="98"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="101"/>
-      <x:c r="B75" s="102"/>
-      <x:c r="C75" s="102"/>
-      <x:c r="D75" s="102"/>
-      <x:c r="E75" s="103"/>
+      <x:c r="A75" s="96"/>
+      <x:c r="B75" s="97"/>
+      <x:c r="C75" s="97"/>
+      <x:c r="D75" s="97"/>
+      <x:c r="E75" s="98"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="101"/>
-      <x:c r="B76" s="102"/>
-      <x:c r="C76" s="102"/>
-      <x:c r="D76" s="102"/>
-      <x:c r="E76" s="103"/>
+      <x:c r="A76" s="96"/>
+      <x:c r="B76" s="97"/>
+      <x:c r="C76" s="97"/>
+      <x:c r="D76" s="97"/>
+      <x:c r="E76" s="98"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="101"/>
-      <x:c r="B77" s="102"/>
-      <x:c r="C77" s="102"/>
-      <x:c r="D77" s="102"/>
-      <x:c r="E77" s="103"/>
+      <x:c r="A77" s="96"/>
+      <x:c r="B77" s="97"/>
+      <x:c r="C77" s="97"/>
+      <x:c r="D77" s="97"/>
+      <x:c r="E77" s="98"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="101"/>
-      <x:c r="B78" s="102"/>
-      <x:c r="C78" s="102"/>
-      <x:c r="D78" s="102"/>
-      <x:c r="E78" s="103"/>
+      <x:c r="A78" s="96"/>
+      <x:c r="B78" s="97"/>
+      <x:c r="C78" s="97"/>
+      <x:c r="D78" s="97"/>
+      <x:c r="E78" s="98"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="101"/>
-      <x:c r="B79" s="102"/>
-      <x:c r="C79" s="102"/>
-      <x:c r="D79" s="102"/>
-      <x:c r="E79" s="103"/>
+      <x:c r="A79" s="96"/>
+      <x:c r="B79" s="97"/>
+      <x:c r="C79" s="97"/>
+      <x:c r="D79" s="97"/>
+      <x:c r="E79" s="98"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="101"/>
-      <x:c r="B80" s="102"/>
-      <x:c r="C80" s="102"/>
-      <x:c r="D80" s="102"/>
-      <x:c r="E80" s="103"/>
+      <x:c r="A80" s="96"/>
+      <x:c r="B80" s="97"/>
+      <x:c r="C80" s="97"/>
+      <x:c r="D80" s="97"/>
+      <x:c r="E80" s="98"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="101"/>
-      <x:c r="B81" s="102"/>
-      <x:c r="C81" s="102"/>
-      <x:c r="D81" s="102"/>
-      <x:c r="E81" s="103"/>
+      <x:c r="A81" s="96"/>
+      <x:c r="B81" s="97"/>
+      <x:c r="C81" s="97"/>
+      <x:c r="D81" s="97"/>
+      <x:c r="E81" s="98"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="101"/>
-      <x:c r="B82" s="102"/>
-      <x:c r="C82" s="102"/>
-      <x:c r="D82" s="102"/>
-      <x:c r="E82" s="103"/>
+      <x:c r="A82" s="96"/>
+      <x:c r="B82" s="97"/>
+      <x:c r="C82" s="97"/>
+      <x:c r="D82" s="97"/>
+      <x:c r="E82" s="98"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="101"/>
-      <x:c r="B83" s="102"/>
-      <x:c r="C83" s="102"/>
-      <x:c r="D83" s="102"/>
-      <x:c r="E83" s="103"/>
+      <x:c r="A83" s="96"/>
+      <x:c r="B83" s="97"/>
+      <x:c r="C83" s="97"/>
+      <x:c r="D83" s="97"/>
+      <x:c r="E83" s="98"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="101"/>
-      <x:c r="B84" s="102"/>
-      <x:c r="C84" s="102"/>
-      <x:c r="D84" s="102"/>
-      <x:c r="E84" s="103"/>
+      <x:c r="A84" s="96"/>
+      <x:c r="B84" s="97"/>
+      <x:c r="C84" s="97"/>
+      <x:c r="D84" s="97"/>
+      <x:c r="E84" s="98"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="101"/>
-      <x:c r="B85" s="102"/>
-      <x:c r="C85" s="102"/>
-      <x:c r="D85" s="102"/>
-      <x:c r="E85" s="103"/>
+      <x:c r="A85" s="96"/>
+      <x:c r="B85" s="97"/>
+      <x:c r="C85" s="97"/>
+      <x:c r="D85" s="97"/>
+      <x:c r="E85" s="98"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="101"/>
-      <x:c r="B86" s="102"/>
-      <x:c r="C86" s="102"/>
-      <x:c r="D86" s="102"/>
-      <x:c r="E86" s="103"/>
+      <x:c r="A86" s="96"/>
+      <x:c r="B86" s="97"/>
+      <x:c r="C86" s="97"/>
+      <x:c r="D86" s="97"/>
+      <x:c r="E86" s="98"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="101"/>
-      <x:c r="B87" s="102"/>
-      <x:c r="C87" s="102"/>
-      <x:c r="D87" s="102"/>
-      <x:c r="E87" s="103"/>
+      <x:c r="A87" s="96"/>
+      <x:c r="B87" s="97"/>
+      <x:c r="C87" s="97"/>
+      <x:c r="D87" s="97"/>
+      <x:c r="E87" s="98"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="101"/>
-      <x:c r="B88" s="102"/>
-      <x:c r="C88" s="102"/>
-      <x:c r="D88" s="102"/>
-      <x:c r="E88" s="103"/>
+      <x:c r="A88" s="96"/>
+      <x:c r="B88" s="97"/>
+      <x:c r="C88" s="97"/>
+      <x:c r="D88" s="97"/>
+      <x:c r="E88" s="98"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="101"/>
-      <x:c r="B89" s="102"/>
-      <x:c r="C89" s="102"/>
-      <x:c r="D89" s="102"/>
-      <x:c r="E89" s="103"/>
+      <x:c r="A89" s="96"/>
+      <x:c r="B89" s="97"/>
+      <x:c r="C89" s="97"/>
+      <x:c r="D89" s="97"/>
+      <x:c r="E89" s="98"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="101"/>
-      <x:c r="B90" s="102"/>
-      <x:c r="C90" s="102"/>
-      <x:c r="D90" s="102"/>
-      <x:c r="E90" s="103"/>
+      <x:c r="A90" s="96"/>
+      <x:c r="B90" s="97"/>
+      <x:c r="C90" s="97"/>
+      <x:c r="D90" s="97"/>
+      <x:c r="E90" s="98"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="101"/>
-      <x:c r="B91" s="102"/>
-      <x:c r="C91" s="102"/>
-      <x:c r="D91" s="102"/>
-      <x:c r="E91" s="103"/>
+      <x:c r="A91" s="96"/>
+      <x:c r="B91" s="97"/>
+      <x:c r="C91" s="97"/>
+      <x:c r="D91" s="97"/>
+      <x:c r="E91" s="98"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="101"/>
-      <x:c r="B92" s="102"/>
-      <x:c r="C92" s="102"/>
-      <x:c r="D92" s="102"/>
-      <x:c r="E92" s="103"/>
+      <x:c r="A92" s="96"/>
+      <x:c r="B92" s="97"/>
+      <x:c r="C92" s="97"/>
+      <x:c r="D92" s="97"/>
+      <x:c r="E92" s="98"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="101"/>
-      <x:c r="B93" s="102"/>
-      <x:c r="C93" s="102"/>
-      <x:c r="D93" s="102"/>
-      <x:c r="E93" s="103"/>
+      <x:c r="A93" s="96"/>
+      <x:c r="B93" s="97"/>
+      <x:c r="C93" s="97"/>
+      <x:c r="D93" s="97"/>
+      <x:c r="E93" s="98"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="101"/>
-      <x:c r="B94" s="102"/>
-      <x:c r="C94" s="102"/>
-      <x:c r="D94" s="102"/>
-      <x:c r="E94" s="103"/>
+      <x:c r="A94" s="96"/>
+      <x:c r="B94" s="97"/>
+      <x:c r="C94" s="97"/>
+      <x:c r="D94" s="97"/>
+      <x:c r="E94" s="98"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="101"/>
-      <x:c r="B95" s="102"/>
-      <x:c r="C95" s="102"/>
-      <x:c r="D95" s="102"/>
-      <x:c r="E95" s="103"/>
+      <x:c r="A95" s="96"/>
+      <x:c r="B95" s="97"/>
+      <x:c r="C95" s="97"/>
+      <x:c r="D95" s="97"/>
+      <x:c r="E95" s="98"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="101"/>
-      <x:c r="B96" s="102"/>
-      <x:c r="C96" s="102"/>
-      <x:c r="D96" s="102"/>
-      <x:c r="E96" s="103"/>
+      <x:c r="A96" s="96"/>
+      <x:c r="B96" s="97"/>
+      <x:c r="C96" s="97"/>
+      <x:c r="D96" s="97"/>
+      <x:c r="E96" s="98"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="101"/>
-      <x:c r="B97" s="102"/>
-      <x:c r="C97" s="102"/>
-      <x:c r="D97" s="102"/>
-      <x:c r="E97" s="103"/>
+      <x:c r="A97" s="96"/>
+      <x:c r="B97" s="97"/>
+      <x:c r="C97" s="97"/>
+      <x:c r="D97" s="97"/>
+      <x:c r="E97" s="98"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="101"/>
-      <x:c r="B98" s="102"/>
-      <x:c r="C98" s="102"/>
-      <x:c r="D98" s="102"/>
-      <x:c r="E98" s="103"/>
+      <x:c r="A98" s="96"/>
+      <x:c r="B98" s="97"/>
+      <x:c r="C98" s="97"/>
+      <x:c r="D98" s="97"/>
+      <x:c r="E98" s="98"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="101"/>
-      <x:c r="B99" s="102"/>
-      <x:c r="C99" s="102"/>
-      <x:c r="D99" s="102"/>
-      <x:c r="E99" s="103"/>
+      <x:c r="A99" s="96"/>
+      <x:c r="B99" s="97"/>
+      <x:c r="C99" s="97"/>
+      <x:c r="D99" s="97"/>
+      <x:c r="E99" s="98"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="101"/>
-      <x:c r="B100" s="102"/>
-      <x:c r="C100" s="102"/>
-      <x:c r="D100" s="102"/>
-      <x:c r="E100" s="103"/>
+      <x:c r="A100" s="96"/>
+      <x:c r="B100" s="97"/>
+      <x:c r="C100" s="97"/>
+      <x:c r="D100" s="97"/>
+      <x:c r="E100" s="98"/>
     </x:row>
     <x:row r="101">
-      <x:c r="A101" s="101"/>
-      <x:c r="B101" s="102"/>
-      <x:c r="C101" s="102"/>
-      <x:c r="D101" s="102"/>
-      <x:c r="E101" s="103"/>
+      <x:c r="A101" s="96"/>
+      <x:c r="B101" s="97"/>
+      <x:c r="C101" s="97"/>
+      <x:c r="D101" s="97"/>
+      <x:c r="E101" s="98"/>
     </x:row>
     <x:row r="102">
-      <x:c r="A102" s="101"/>
-      <x:c r="B102" s="102"/>
-      <x:c r="C102" s="102"/>
-      <x:c r="D102" s="102"/>
-      <x:c r="E102" s="103"/>
+      <x:c r="A102" s="96"/>
+      <x:c r="B102" s="97"/>
+      <x:c r="C102" s="97"/>
+      <x:c r="D102" s="97"/>
+      <x:c r="E102" s="98"/>
     </x:row>
     <x:row r="103">
-      <x:c r="A103" s="101"/>
-      <x:c r="B103" s="102"/>
-      <x:c r="C103" s="102"/>
-      <x:c r="D103" s="102"/>
-      <x:c r="E103" s="103"/>
+      <x:c r="A103" s="96"/>
+      <x:c r="B103" s="97"/>
+      <x:c r="C103" s="97"/>
+      <x:c r="D103" s="97"/>
+      <x:c r="E103" s="98"/>
     </x:row>
     <x:row r="104">
-      <x:c r="A104" s="104"/>
-      <x:c r="B104" s="105"/>
-      <x:c r="C104" s="105"/>
-      <x:c r="D104" s="105"/>
-      <x:c r="E104" s="106"/>
+      <x:c r="A104" s="99"/>
+      <x:c r="B104" s="100"/>
+      <x:c r="C104" s="100"/>
+      <x:c r="D104" s="100"/>
+      <x:c r="E104" s="101"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2222,6 +2259,1855 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF70AD47"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="23" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="23" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="38" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="22" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="23" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="2"/>
+      <x:c r="B1" s="2"/>
+      <x:c r="C1" s="2"/>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
+      <x:c r="J1" s="2"/>
+      <x:c r="K1" s="2"/>
+      <x:c r="L1" s="2"/>
+      <x:c r="M1" s="2"/>
+      <x:c r="N1" s="2"/>
+      <x:c r="O1" s="2"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="3" t="str">
+        <x:v>循环定时任务</x:v>
+      </x:c>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+      <x:c r="I2" s="2"/>
+      <x:c r="J2" s="2"/>
+      <x:c r="K2" s="2"/>
+      <x:c r="L2" s="2"/>
+      <x:c r="M2" s="2"/>
+      <x:c r="N2" s="2"/>
+      <x:c r="O2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="4" t="str">
+        <x:v>Excel 必须保持打开、Windows 用户必须保持登录且电脑不能休眠。计划时间一旦过去即标记“已错过”，不补发。</x:v>
+      </x:c>
+      <x:c r="B3" s="4"/>
+      <x:c r="C3" s="4"/>
+      <x:c r="D3" s="4"/>
+      <x:c r="E3" s="4"/>
+      <x:c r="F3" s="4"/>
+      <x:c r="G3" s="4"/>
+      <x:c r="H3" s="4"/>
+      <x:c r="I3" s="4"/>
+      <x:c r="J3" s="4"/>
+      <x:c r="K3" s="4"/>
+      <x:c r="L3" s="4"/>
+      <x:c r="M3" s="4"/>
+      <x:c r="N3" s="4"/>
+      <x:c r="O3" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+      <x:c r="I4" s="2"/>
+      <x:c r="J4" s="2"/>
+      <x:c r="K4" s="2"/>
+      <x:c r="L4" s="2"/>
+      <x:c r="M4" s="2"/>
+      <x:c r="N4" s="2"/>
+      <x:c r="O4" s="2"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="20" t="str">
+        <x:v>任务 ID</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>任务名称</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>启用</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>模板</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="str">
+        <x:v>频率</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="str">
+        <x:v>星期</x:v>
+      </x:c>
+      <x:c r="G5" s="20" t="str">
+        <x:v>发送时间</x:v>
+      </x:c>
+      <x:c r="H5" s="20" t="str">
+        <x:v>参数快照</x:v>
+      </x:c>
+      <x:c r="I5" s="20" t="str">
+        <x:v>模板签名</x:v>
+      </x:c>
+      <x:c r="J5" s="20" t="str">
+        <x:v>下一次发送</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="str">
+        <x:v>上次计划时间</x:v>
+      </x:c>
+      <x:c r="L5" s="20" t="str">
+        <x:v>上次结果</x:v>
+      </x:c>
+      <x:c r="M5" s="20" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+      <x:c r="N5" s="20" t="str">
+        <x:v>发生键</x:v>
+      </x:c>
+      <x:c r="O5" s="20" t="str">
+        <x:v>更新时间</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="22" customHeight="1">
+      <x:c r="A6" s="102"/>
+      <x:c r="B6" s="76"/>
+      <x:c r="C6" s="76"/>
+      <x:c r="D6" s="76"/>
+      <x:c r="E6" s="76"/>
+      <x:c r="F6" s="76"/>
+      <x:c r="G6" s="111"/>
+      <x:c r="H6" s="105"/>
+      <x:c r="I6" s="105"/>
+      <x:c r="J6" s="114"/>
+      <x:c r="K6" s="114"/>
+      <x:c r="L6" s="105"/>
+      <x:c r="M6" s="105"/>
+      <x:c r="N6" s="105"/>
+      <x:c r="O6" s="117"/>
+    </x:row>
+    <x:row r="7" ht="22" customHeight="1">
+      <x:c r="A7" s="103"/>
+      <x:c r="B7" s="79"/>
+      <x:c r="C7" s="79"/>
+      <x:c r="D7" s="79"/>
+      <x:c r="E7" s="79"/>
+      <x:c r="F7" s="79"/>
+      <x:c r="G7" s="112"/>
+      <x:c r="H7" s="107"/>
+      <x:c r="I7" s="107"/>
+      <x:c r="J7" s="115"/>
+      <x:c r="K7" s="115"/>
+      <x:c r="L7" s="107"/>
+      <x:c r="M7" s="107"/>
+      <x:c r="N7" s="107"/>
+      <x:c r="O7" s="118"/>
+    </x:row>
+    <x:row r="8" ht="22" customHeight="1">
+      <x:c r="A8" s="103"/>
+      <x:c r="B8" s="79"/>
+      <x:c r="C8" s="79"/>
+      <x:c r="D8" s="79"/>
+      <x:c r="E8" s="79"/>
+      <x:c r="F8" s="79"/>
+      <x:c r="G8" s="112"/>
+      <x:c r="H8" s="107"/>
+      <x:c r="I8" s="107"/>
+      <x:c r="J8" s="115"/>
+      <x:c r="K8" s="115"/>
+      <x:c r="L8" s="107"/>
+      <x:c r="M8" s="107"/>
+      <x:c r="N8" s="107"/>
+      <x:c r="O8" s="118"/>
+    </x:row>
+    <x:row r="9" ht="22" customHeight="1">
+      <x:c r="A9" s="103"/>
+      <x:c r="B9" s="79"/>
+      <x:c r="C9" s="79"/>
+      <x:c r="D9" s="79"/>
+      <x:c r="E9" s="79"/>
+      <x:c r="F9" s="79"/>
+      <x:c r="G9" s="112"/>
+      <x:c r="H9" s="107"/>
+      <x:c r="I9" s="107"/>
+      <x:c r="J9" s="115"/>
+      <x:c r="K9" s="115"/>
+      <x:c r="L9" s="107"/>
+      <x:c r="M9" s="107"/>
+      <x:c r="N9" s="107"/>
+      <x:c r="O9" s="118"/>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="103"/>
+      <x:c r="B10" s="79"/>
+      <x:c r="C10" s="79"/>
+      <x:c r="D10" s="79"/>
+      <x:c r="E10" s="79"/>
+      <x:c r="F10" s="79"/>
+      <x:c r="G10" s="112"/>
+      <x:c r="H10" s="107"/>
+      <x:c r="I10" s="107"/>
+      <x:c r="J10" s="115"/>
+      <x:c r="K10" s="115"/>
+      <x:c r="L10" s="107"/>
+      <x:c r="M10" s="107"/>
+      <x:c r="N10" s="107"/>
+      <x:c r="O10" s="118"/>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="103"/>
+      <x:c r="B11" s="79"/>
+      <x:c r="C11" s="79"/>
+      <x:c r="D11" s="79"/>
+      <x:c r="E11" s="79"/>
+      <x:c r="F11" s="79"/>
+      <x:c r="G11" s="112"/>
+      <x:c r="H11" s="107"/>
+      <x:c r="I11" s="107"/>
+      <x:c r="J11" s="115"/>
+      <x:c r="K11" s="115"/>
+      <x:c r="L11" s="107"/>
+      <x:c r="M11" s="107"/>
+      <x:c r="N11" s="107"/>
+      <x:c r="O11" s="118"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="103"/>
+      <x:c r="B12" s="79"/>
+      <x:c r="C12" s="79"/>
+      <x:c r="D12" s="79"/>
+      <x:c r="E12" s="79"/>
+      <x:c r="F12" s="79"/>
+      <x:c r="G12" s="112"/>
+      <x:c r="H12" s="107"/>
+      <x:c r="I12" s="107"/>
+      <x:c r="J12" s="115"/>
+      <x:c r="K12" s="115"/>
+      <x:c r="L12" s="107"/>
+      <x:c r="M12" s="107"/>
+      <x:c r="N12" s="107"/>
+      <x:c r="O12" s="118"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="103"/>
+      <x:c r="B13" s="79"/>
+      <x:c r="C13" s="79"/>
+      <x:c r="D13" s="79"/>
+      <x:c r="E13" s="79"/>
+      <x:c r="F13" s="79"/>
+      <x:c r="G13" s="112"/>
+      <x:c r="H13" s="107"/>
+      <x:c r="I13" s="107"/>
+      <x:c r="J13" s="115"/>
+      <x:c r="K13" s="115"/>
+      <x:c r="L13" s="107"/>
+      <x:c r="M13" s="107"/>
+      <x:c r="N13" s="107"/>
+      <x:c r="O13" s="118"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="103"/>
+      <x:c r="B14" s="79"/>
+      <x:c r="C14" s="79"/>
+      <x:c r="D14" s="79"/>
+      <x:c r="E14" s="79"/>
+      <x:c r="F14" s="79"/>
+      <x:c r="G14" s="112"/>
+      <x:c r="H14" s="107"/>
+      <x:c r="I14" s="107"/>
+      <x:c r="J14" s="115"/>
+      <x:c r="K14" s="115"/>
+      <x:c r="L14" s="107"/>
+      <x:c r="M14" s="107"/>
+      <x:c r="N14" s="107"/>
+      <x:c r="O14" s="118"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="103"/>
+      <x:c r="B15" s="79"/>
+      <x:c r="C15" s="79"/>
+      <x:c r="D15" s="79"/>
+      <x:c r="E15" s="79"/>
+      <x:c r="F15" s="79"/>
+      <x:c r="G15" s="112"/>
+      <x:c r="H15" s="107"/>
+      <x:c r="I15" s="107"/>
+      <x:c r="J15" s="115"/>
+      <x:c r="K15" s="115"/>
+      <x:c r="L15" s="107"/>
+      <x:c r="M15" s="107"/>
+      <x:c r="N15" s="107"/>
+      <x:c r="O15" s="118"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="103"/>
+      <x:c r="B16" s="79"/>
+      <x:c r="C16" s="79"/>
+      <x:c r="D16" s="79"/>
+      <x:c r="E16" s="79"/>
+      <x:c r="F16" s="79"/>
+      <x:c r="G16" s="112"/>
+      <x:c r="H16" s="107"/>
+      <x:c r="I16" s="107"/>
+      <x:c r="J16" s="115"/>
+      <x:c r="K16" s="115"/>
+      <x:c r="L16" s="107"/>
+      <x:c r="M16" s="107"/>
+      <x:c r="N16" s="107"/>
+      <x:c r="O16" s="118"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="103"/>
+      <x:c r="B17" s="79"/>
+      <x:c r="C17" s="79"/>
+      <x:c r="D17" s="79"/>
+      <x:c r="E17" s="79"/>
+      <x:c r="F17" s="79"/>
+      <x:c r="G17" s="112"/>
+      <x:c r="H17" s="107"/>
+      <x:c r="I17" s="107"/>
+      <x:c r="J17" s="115"/>
+      <x:c r="K17" s="115"/>
+      <x:c r="L17" s="107"/>
+      <x:c r="M17" s="107"/>
+      <x:c r="N17" s="107"/>
+      <x:c r="O17" s="118"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="103"/>
+      <x:c r="B18" s="79"/>
+      <x:c r="C18" s="79"/>
+      <x:c r="D18" s="79"/>
+      <x:c r="E18" s="79"/>
+      <x:c r="F18" s="79"/>
+      <x:c r="G18" s="112"/>
+      <x:c r="H18" s="107"/>
+      <x:c r="I18" s="107"/>
+      <x:c r="J18" s="115"/>
+      <x:c r="K18" s="115"/>
+      <x:c r="L18" s="107"/>
+      <x:c r="M18" s="107"/>
+      <x:c r="N18" s="107"/>
+      <x:c r="O18" s="118"/>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19" s="103"/>
+      <x:c r="B19" s="79"/>
+      <x:c r="C19" s="79"/>
+      <x:c r="D19" s="79"/>
+      <x:c r="E19" s="79"/>
+      <x:c r="F19" s="79"/>
+      <x:c r="G19" s="112"/>
+      <x:c r="H19" s="107"/>
+      <x:c r="I19" s="107"/>
+      <x:c r="J19" s="115"/>
+      <x:c r="K19" s="115"/>
+      <x:c r="L19" s="107"/>
+      <x:c r="M19" s="107"/>
+      <x:c r="N19" s="107"/>
+      <x:c r="O19" s="118"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="103"/>
+      <x:c r="B20" s="79"/>
+      <x:c r="C20" s="79"/>
+      <x:c r="D20" s="79"/>
+      <x:c r="E20" s="79"/>
+      <x:c r="F20" s="79"/>
+      <x:c r="G20" s="112"/>
+      <x:c r="H20" s="107"/>
+      <x:c r="I20" s="107"/>
+      <x:c r="J20" s="115"/>
+      <x:c r="K20" s="115"/>
+      <x:c r="L20" s="107"/>
+      <x:c r="M20" s="107"/>
+      <x:c r="N20" s="107"/>
+      <x:c r="O20" s="118"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="103"/>
+      <x:c r="B21" s="79"/>
+      <x:c r="C21" s="79"/>
+      <x:c r="D21" s="79"/>
+      <x:c r="E21" s="79"/>
+      <x:c r="F21" s="79"/>
+      <x:c r="G21" s="112"/>
+      <x:c r="H21" s="107"/>
+      <x:c r="I21" s="107"/>
+      <x:c r="J21" s="115"/>
+      <x:c r="K21" s="115"/>
+      <x:c r="L21" s="107"/>
+      <x:c r="M21" s="107"/>
+      <x:c r="N21" s="107"/>
+      <x:c r="O21" s="118"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="103"/>
+      <x:c r="B22" s="79"/>
+      <x:c r="C22" s="79"/>
+      <x:c r="D22" s="79"/>
+      <x:c r="E22" s="79"/>
+      <x:c r="F22" s="79"/>
+      <x:c r="G22" s="112"/>
+      <x:c r="H22" s="107"/>
+      <x:c r="I22" s="107"/>
+      <x:c r="J22" s="115"/>
+      <x:c r="K22" s="115"/>
+      <x:c r="L22" s="107"/>
+      <x:c r="M22" s="107"/>
+      <x:c r="N22" s="107"/>
+      <x:c r="O22" s="118"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="103"/>
+      <x:c r="B23" s="79"/>
+      <x:c r="C23" s="79"/>
+      <x:c r="D23" s="79"/>
+      <x:c r="E23" s="79"/>
+      <x:c r="F23" s="79"/>
+      <x:c r="G23" s="112"/>
+      <x:c r="H23" s="107"/>
+      <x:c r="I23" s="107"/>
+      <x:c r="J23" s="115"/>
+      <x:c r="K23" s="115"/>
+      <x:c r="L23" s="107"/>
+      <x:c r="M23" s="107"/>
+      <x:c r="N23" s="107"/>
+      <x:c r="O23" s="118"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="103"/>
+      <x:c r="B24" s="79"/>
+      <x:c r="C24" s="79"/>
+      <x:c r="D24" s="79"/>
+      <x:c r="E24" s="79"/>
+      <x:c r="F24" s="79"/>
+      <x:c r="G24" s="112"/>
+      <x:c r="H24" s="107"/>
+      <x:c r="I24" s="107"/>
+      <x:c r="J24" s="115"/>
+      <x:c r="K24" s="115"/>
+      <x:c r="L24" s="107"/>
+      <x:c r="M24" s="107"/>
+      <x:c r="N24" s="107"/>
+      <x:c r="O24" s="118"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="103"/>
+      <x:c r="B25" s="79"/>
+      <x:c r="C25" s="79"/>
+      <x:c r="D25" s="79"/>
+      <x:c r="E25" s="79"/>
+      <x:c r="F25" s="79"/>
+      <x:c r="G25" s="112"/>
+      <x:c r="H25" s="107"/>
+      <x:c r="I25" s="107"/>
+      <x:c r="J25" s="115"/>
+      <x:c r="K25" s="115"/>
+      <x:c r="L25" s="107"/>
+      <x:c r="M25" s="107"/>
+      <x:c r="N25" s="107"/>
+      <x:c r="O25" s="118"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="103"/>
+      <x:c r="B26" s="79"/>
+      <x:c r="C26" s="79"/>
+      <x:c r="D26" s="79"/>
+      <x:c r="E26" s="79"/>
+      <x:c r="F26" s="79"/>
+      <x:c r="G26" s="112"/>
+      <x:c r="H26" s="107"/>
+      <x:c r="I26" s="107"/>
+      <x:c r="J26" s="115"/>
+      <x:c r="K26" s="115"/>
+      <x:c r="L26" s="107"/>
+      <x:c r="M26" s="107"/>
+      <x:c r="N26" s="107"/>
+      <x:c r="O26" s="118"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="103"/>
+      <x:c r="B27" s="79"/>
+      <x:c r="C27" s="79"/>
+      <x:c r="D27" s="79"/>
+      <x:c r="E27" s="79"/>
+      <x:c r="F27" s="79"/>
+      <x:c r="G27" s="112"/>
+      <x:c r="H27" s="107"/>
+      <x:c r="I27" s="107"/>
+      <x:c r="J27" s="115"/>
+      <x:c r="K27" s="115"/>
+      <x:c r="L27" s="107"/>
+      <x:c r="M27" s="107"/>
+      <x:c r="N27" s="107"/>
+      <x:c r="O27" s="118"/>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" s="103"/>
+      <x:c r="B28" s="79"/>
+      <x:c r="C28" s="79"/>
+      <x:c r="D28" s="79"/>
+      <x:c r="E28" s="79"/>
+      <x:c r="F28" s="79"/>
+      <x:c r="G28" s="112"/>
+      <x:c r="H28" s="107"/>
+      <x:c r="I28" s="107"/>
+      <x:c r="J28" s="115"/>
+      <x:c r="K28" s="115"/>
+      <x:c r="L28" s="107"/>
+      <x:c r="M28" s="107"/>
+      <x:c r="N28" s="107"/>
+      <x:c r="O28" s="118"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" s="103"/>
+      <x:c r="B29" s="79"/>
+      <x:c r="C29" s="79"/>
+      <x:c r="D29" s="79"/>
+      <x:c r="E29" s="79"/>
+      <x:c r="F29" s="79"/>
+      <x:c r="G29" s="112"/>
+      <x:c r="H29" s="107"/>
+      <x:c r="I29" s="107"/>
+      <x:c r="J29" s="115"/>
+      <x:c r="K29" s="115"/>
+      <x:c r="L29" s="107"/>
+      <x:c r="M29" s="107"/>
+      <x:c r="N29" s="107"/>
+      <x:c r="O29" s="118"/>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
+      <x:c r="A30" s="103"/>
+      <x:c r="B30" s="79"/>
+      <x:c r="C30" s="79"/>
+      <x:c r="D30" s="79"/>
+      <x:c r="E30" s="79"/>
+      <x:c r="F30" s="79"/>
+      <x:c r="G30" s="112"/>
+      <x:c r="H30" s="107"/>
+      <x:c r="I30" s="107"/>
+      <x:c r="J30" s="115"/>
+      <x:c r="K30" s="115"/>
+      <x:c r="L30" s="107"/>
+      <x:c r="M30" s="107"/>
+      <x:c r="N30" s="107"/>
+      <x:c r="O30" s="118"/>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
+      <x:c r="A31" s="103"/>
+      <x:c r="B31" s="79"/>
+      <x:c r="C31" s="79"/>
+      <x:c r="D31" s="79"/>
+      <x:c r="E31" s="79"/>
+      <x:c r="F31" s="79"/>
+      <x:c r="G31" s="112"/>
+      <x:c r="H31" s="107"/>
+      <x:c r="I31" s="107"/>
+      <x:c r="J31" s="115"/>
+      <x:c r="K31" s="115"/>
+      <x:c r="L31" s="107"/>
+      <x:c r="M31" s="107"/>
+      <x:c r="N31" s="107"/>
+      <x:c r="O31" s="118"/>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
+      <x:c r="A32" s="103"/>
+      <x:c r="B32" s="79"/>
+      <x:c r="C32" s="79"/>
+      <x:c r="D32" s="79"/>
+      <x:c r="E32" s="79"/>
+      <x:c r="F32" s="79"/>
+      <x:c r="G32" s="112"/>
+      <x:c r="H32" s="107"/>
+      <x:c r="I32" s="107"/>
+      <x:c r="J32" s="115"/>
+      <x:c r="K32" s="115"/>
+      <x:c r="L32" s="107"/>
+      <x:c r="M32" s="107"/>
+      <x:c r="N32" s="107"/>
+      <x:c r="O32" s="118"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="103"/>
+      <x:c r="B33" s="79"/>
+      <x:c r="C33" s="79"/>
+      <x:c r="D33" s="79"/>
+      <x:c r="E33" s="79"/>
+      <x:c r="F33" s="79"/>
+      <x:c r="G33" s="112"/>
+      <x:c r="H33" s="107"/>
+      <x:c r="I33" s="107"/>
+      <x:c r="J33" s="115"/>
+      <x:c r="K33" s="115"/>
+      <x:c r="L33" s="107"/>
+      <x:c r="M33" s="107"/>
+      <x:c r="N33" s="107"/>
+      <x:c r="O33" s="118"/>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="103"/>
+      <x:c r="B34" s="79"/>
+      <x:c r="C34" s="79"/>
+      <x:c r="D34" s="79"/>
+      <x:c r="E34" s="79"/>
+      <x:c r="F34" s="79"/>
+      <x:c r="G34" s="112"/>
+      <x:c r="H34" s="107"/>
+      <x:c r="I34" s="107"/>
+      <x:c r="J34" s="115"/>
+      <x:c r="K34" s="115"/>
+      <x:c r="L34" s="107"/>
+      <x:c r="M34" s="107"/>
+      <x:c r="N34" s="107"/>
+      <x:c r="O34" s="118"/>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35" s="103"/>
+      <x:c r="B35" s="79"/>
+      <x:c r="C35" s="79"/>
+      <x:c r="D35" s="79"/>
+      <x:c r="E35" s="79"/>
+      <x:c r="F35" s="79"/>
+      <x:c r="G35" s="112"/>
+      <x:c r="H35" s="107"/>
+      <x:c r="I35" s="107"/>
+      <x:c r="J35" s="115"/>
+      <x:c r="K35" s="115"/>
+      <x:c r="L35" s="107"/>
+      <x:c r="M35" s="107"/>
+      <x:c r="N35" s="107"/>
+      <x:c r="O35" s="118"/>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36" s="103"/>
+      <x:c r="B36" s="79"/>
+      <x:c r="C36" s="79"/>
+      <x:c r="D36" s="79"/>
+      <x:c r="E36" s="79"/>
+      <x:c r="F36" s="79"/>
+      <x:c r="G36" s="112"/>
+      <x:c r="H36" s="107"/>
+      <x:c r="I36" s="107"/>
+      <x:c r="J36" s="115"/>
+      <x:c r="K36" s="115"/>
+      <x:c r="L36" s="107"/>
+      <x:c r="M36" s="107"/>
+      <x:c r="N36" s="107"/>
+      <x:c r="O36" s="118"/>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="103"/>
+      <x:c r="B37" s="79"/>
+      <x:c r="C37" s="79"/>
+      <x:c r="D37" s="79"/>
+      <x:c r="E37" s="79"/>
+      <x:c r="F37" s="79"/>
+      <x:c r="G37" s="112"/>
+      <x:c r="H37" s="107"/>
+      <x:c r="I37" s="107"/>
+      <x:c r="J37" s="115"/>
+      <x:c r="K37" s="115"/>
+      <x:c r="L37" s="107"/>
+      <x:c r="M37" s="107"/>
+      <x:c r="N37" s="107"/>
+      <x:c r="O37" s="118"/>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="103"/>
+      <x:c r="B38" s="79"/>
+      <x:c r="C38" s="79"/>
+      <x:c r="D38" s="79"/>
+      <x:c r="E38" s="79"/>
+      <x:c r="F38" s="79"/>
+      <x:c r="G38" s="112"/>
+      <x:c r="H38" s="107"/>
+      <x:c r="I38" s="107"/>
+      <x:c r="J38" s="115"/>
+      <x:c r="K38" s="115"/>
+      <x:c r="L38" s="107"/>
+      <x:c r="M38" s="107"/>
+      <x:c r="N38" s="107"/>
+      <x:c r="O38" s="118"/>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
+      <x:c r="A39" s="103"/>
+      <x:c r="B39" s="79"/>
+      <x:c r="C39" s="79"/>
+      <x:c r="D39" s="79"/>
+      <x:c r="E39" s="79"/>
+      <x:c r="F39" s="79"/>
+      <x:c r="G39" s="112"/>
+      <x:c r="H39" s="107"/>
+      <x:c r="I39" s="107"/>
+      <x:c r="J39" s="115"/>
+      <x:c r="K39" s="115"/>
+      <x:c r="L39" s="107"/>
+      <x:c r="M39" s="107"/>
+      <x:c r="N39" s="107"/>
+      <x:c r="O39" s="118"/>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
+      <x:c r="A40" s="103"/>
+      <x:c r="B40" s="79"/>
+      <x:c r="C40" s="79"/>
+      <x:c r="D40" s="79"/>
+      <x:c r="E40" s="79"/>
+      <x:c r="F40" s="79"/>
+      <x:c r="G40" s="112"/>
+      <x:c r="H40" s="107"/>
+      <x:c r="I40" s="107"/>
+      <x:c r="J40" s="115"/>
+      <x:c r="K40" s="115"/>
+      <x:c r="L40" s="107"/>
+      <x:c r="M40" s="107"/>
+      <x:c r="N40" s="107"/>
+      <x:c r="O40" s="118"/>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
+      <x:c r="A41" s="103"/>
+      <x:c r="B41" s="79"/>
+      <x:c r="C41" s="79"/>
+      <x:c r="D41" s="79"/>
+      <x:c r="E41" s="79"/>
+      <x:c r="F41" s="79"/>
+      <x:c r="G41" s="112"/>
+      <x:c r="H41" s="107"/>
+      <x:c r="I41" s="107"/>
+      <x:c r="J41" s="115"/>
+      <x:c r="K41" s="115"/>
+      <x:c r="L41" s="107"/>
+      <x:c r="M41" s="107"/>
+      <x:c r="N41" s="107"/>
+      <x:c r="O41" s="118"/>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
+      <x:c r="A42" s="103"/>
+      <x:c r="B42" s="79"/>
+      <x:c r="C42" s="79"/>
+      <x:c r="D42" s="79"/>
+      <x:c r="E42" s="79"/>
+      <x:c r="F42" s="79"/>
+      <x:c r="G42" s="112"/>
+      <x:c r="H42" s="107"/>
+      <x:c r="I42" s="107"/>
+      <x:c r="J42" s="115"/>
+      <x:c r="K42" s="115"/>
+      <x:c r="L42" s="107"/>
+      <x:c r="M42" s="107"/>
+      <x:c r="N42" s="107"/>
+      <x:c r="O42" s="118"/>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
+      <x:c r="A43" s="103"/>
+      <x:c r="B43" s="79"/>
+      <x:c r="C43" s="79"/>
+      <x:c r="D43" s="79"/>
+      <x:c r="E43" s="79"/>
+      <x:c r="F43" s="79"/>
+      <x:c r="G43" s="112"/>
+      <x:c r="H43" s="107"/>
+      <x:c r="I43" s="107"/>
+      <x:c r="J43" s="115"/>
+      <x:c r="K43" s="115"/>
+      <x:c r="L43" s="107"/>
+      <x:c r="M43" s="107"/>
+      <x:c r="N43" s="107"/>
+      <x:c r="O43" s="118"/>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
+      <x:c r="A44" s="103"/>
+      <x:c r="B44" s="79"/>
+      <x:c r="C44" s="79"/>
+      <x:c r="D44" s="79"/>
+      <x:c r="E44" s="79"/>
+      <x:c r="F44" s="79"/>
+      <x:c r="G44" s="112"/>
+      <x:c r="H44" s="107"/>
+      <x:c r="I44" s="107"/>
+      <x:c r="J44" s="115"/>
+      <x:c r="K44" s="115"/>
+      <x:c r="L44" s="107"/>
+      <x:c r="M44" s="107"/>
+      <x:c r="N44" s="107"/>
+      <x:c r="O44" s="118"/>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="103"/>
+      <x:c r="B45" s="79"/>
+      <x:c r="C45" s="79"/>
+      <x:c r="D45" s="79"/>
+      <x:c r="E45" s="79"/>
+      <x:c r="F45" s="79"/>
+      <x:c r="G45" s="112"/>
+      <x:c r="H45" s="107"/>
+      <x:c r="I45" s="107"/>
+      <x:c r="J45" s="115"/>
+      <x:c r="K45" s="115"/>
+      <x:c r="L45" s="107"/>
+      <x:c r="M45" s="107"/>
+      <x:c r="N45" s="107"/>
+      <x:c r="O45" s="118"/>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
+      <x:c r="A46" s="103"/>
+      <x:c r="B46" s="79"/>
+      <x:c r="C46" s="79"/>
+      <x:c r="D46" s="79"/>
+      <x:c r="E46" s="79"/>
+      <x:c r="F46" s="79"/>
+      <x:c r="G46" s="112"/>
+      <x:c r="H46" s="107"/>
+      <x:c r="I46" s="107"/>
+      <x:c r="J46" s="115"/>
+      <x:c r="K46" s="115"/>
+      <x:c r="L46" s="107"/>
+      <x:c r="M46" s="107"/>
+      <x:c r="N46" s="107"/>
+      <x:c r="O46" s="118"/>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="103"/>
+      <x:c r="B47" s="79"/>
+      <x:c r="C47" s="79"/>
+      <x:c r="D47" s="79"/>
+      <x:c r="E47" s="79"/>
+      <x:c r="F47" s="79"/>
+      <x:c r="G47" s="112"/>
+      <x:c r="H47" s="107"/>
+      <x:c r="I47" s="107"/>
+      <x:c r="J47" s="115"/>
+      <x:c r="K47" s="115"/>
+      <x:c r="L47" s="107"/>
+      <x:c r="M47" s="107"/>
+      <x:c r="N47" s="107"/>
+      <x:c r="O47" s="118"/>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
+      <x:c r="A48" s="103"/>
+      <x:c r="B48" s="79"/>
+      <x:c r="C48" s="79"/>
+      <x:c r="D48" s="79"/>
+      <x:c r="E48" s="79"/>
+      <x:c r="F48" s="79"/>
+      <x:c r="G48" s="112"/>
+      <x:c r="H48" s="107"/>
+      <x:c r="I48" s="107"/>
+      <x:c r="J48" s="115"/>
+      <x:c r="K48" s="115"/>
+      <x:c r="L48" s="107"/>
+      <x:c r="M48" s="107"/>
+      <x:c r="N48" s="107"/>
+      <x:c r="O48" s="118"/>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="103"/>
+      <x:c r="B49" s="79"/>
+      <x:c r="C49" s="79"/>
+      <x:c r="D49" s="79"/>
+      <x:c r="E49" s="79"/>
+      <x:c r="F49" s="79"/>
+      <x:c r="G49" s="112"/>
+      <x:c r="H49" s="107"/>
+      <x:c r="I49" s="107"/>
+      <x:c r="J49" s="115"/>
+      <x:c r="K49" s="115"/>
+      <x:c r="L49" s="107"/>
+      <x:c r="M49" s="107"/>
+      <x:c r="N49" s="107"/>
+      <x:c r="O49" s="118"/>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="103"/>
+      <x:c r="B50" s="79"/>
+      <x:c r="C50" s="79"/>
+      <x:c r="D50" s="79"/>
+      <x:c r="E50" s="79"/>
+      <x:c r="F50" s="79"/>
+      <x:c r="G50" s="112"/>
+      <x:c r="H50" s="107"/>
+      <x:c r="I50" s="107"/>
+      <x:c r="J50" s="115"/>
+      <x:c r="K50" s="115"/>
+      <x:c r="L50" s="107"/>
+      <x:c r="M50" s="107"/>
+      <x:c r="N50" s="107"/>
+      <x:c r="O50" s="118"/>
+    </x:row>
+    <x:row r="51" ht="22" customHeight="1">
+      <x:c r="A51" s="103"/>
+      <x:c r="B51" s="79"/>
+      <x:c r="C51" s="79"/>
+      <x:c r="D51" s="79"/>
+      <x:c r="E51" s="79"/>
+      <x:c r="F51" s="79"/>
+      <x:c r="G51" s="112"/>
+      <x:c r="H51" s="107"/>
+      <x:c r="I51" s="107"/>
+      <x:c r="J51" s="115"/>
+      <x:c r="K51" s="115"/>
+      <x:c r="L51" s="107"/>
+      <x:c r="M51" s="107"/>
+      <x:c r="N51" s="107"/>
+      <x:c r="O51" s="118"/>
+    </x:row>
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="103"/>
+      <x:c r="B52" s="79"/>
+      <x:c r="C52" s="79"/>
+      <x:c r="D52" s="79"/>
+      <x:c r="E52" s="79"/>
+      <x:c r="F52" s="79"/>
+      <x:c r="G52" s="112"/>
+      <x:c r="H52" s="107"/>
+      <x:c r="I52" s="107"/>
+      <x:c r="J52" s="115"/>
+      <x:c r="K52" s="115"/>
+      <x:c r="L52" s="107"/>
+      <x:c r="M52" s="107"/>
+      <x:c r="N52" s="107"/>
+      <x:c r="O52" s="118"/>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="103"/>
+      <x:c r="B53" s="79"/>
+      <x:c r="C53" s="79"/>
+      <x:c r="D53" s="79"/>
+      <x:c r="E53" s="79"/>
+      <x:c r="F53" s="79"/>
+      <x:c r="G53" s="112"/>
+      <x:c r="H53" s="107"/>
+      <x:c r="I53" s="107"/>
+      <x:c r="J53" s="115"/>
+      <x:c r="K53" s="115"/>
+      <x:c r="L53" s="107"/>
+      <x:c r="M53" s="107"/>
+      <x:c r="N53" s="107"/>
+      <x:c r="O53" s="118"/>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="103"/>
+      <x:c r="B54" s="79"/>
+      <x:c r="C54" s="79"/>
+      <x:c r="D54" s="79"/>
+      <x:c r="E54" s="79"/>
+      <x:c r="F54" s="79"/>
+      <x:c r="G54" s="112"/>
+      <x:c r="H54" s="107"/>
+      <x:c r="I54" s="107"/>
+      <x:c r="J54" s="115"/>
+      <x:c r="K54" s="115"/>
+      <x:c r="L54" s="107"/>
+      <x:c r="M54" s="107"/>
+      <x:c r="N54" s="107"/>
+      <x:c r="O54" s="118"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="103"/>
+      <x:c r="B55" s="79"/>
+      <x:c r="C55" s="79"/>
+      <x:c r="D55" s="79"/>
+      <x:c r="E55" s="79"/>
+      <x:c r="F55" s="79"/>
+      <x:c r="G55" s="112"/>
+      <x:c r="H55" s="107"/>
+      <x:c r="I55" s="107"/>
+      <x:c r="J55" s="115"/>
+      <x:c r="K55" s="115"/>
+      <x:c r="L55" s="107"/>
+      <x:c r="M55" s="107"/>
+      <x:c r="N55" s="107"/>
+      <x:c r="O55" s="118"/>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="103"/>
+      <x:c r="B56" s="79"/>
+      <x:c r="C56" s="79"/>
+      <x:c r="D56" s="79"/>
+      <x:c r="E56" s="79"/>
+      <x:c r="F56" s="79"/>
+      <x:c r="G56" s="112"/>
+      <x:c r="H56" s="107"/>
+      <x:c r="I56" s="107"/>
+      <x:c r="J56" s="115"/>
+      <x:c r="K56" s="115"/>
+      <x:c r="L56" s="107"/>
+      <x:c r="M56" s="107"/>
+      <x:c r="N56" s="107"/>
+      <x:c r="O56" s="118"/>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="103"/>
+      <x:c r="B57" s="79"/>
+      <x:c r="C57" s="79"/>
+      <x:c r="D57" s="79"/>
+      <x:c r="E57" s="79"/>
+      <x:c r="F57" s="79"/>
+      <x:c r="G57" s="112"/>
+      <x:c r="H57" s="107"/>
+      <x:c r="I57" s="107"/>
+      <x:c r="J57" s="115"/>
+      <x:c r="K57" s="115"/>
+      <x:c r="L57" s="107"/>
+      <x:c r="M57" s="107"/>
+      <x:c r="N57" s="107"/>
+      <x:c r="O57" s="118"/>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="103"/>
+      <x:c r="B58" s="79"/>
+      <x:c r="C58" s="79"/>
+      <x:c r="D58" s="79"/>
+      <x:c r="E58" s="79"/>
+      <x:c r="F58" s="79"/>
+      <x:c r="G58" s="112"/>
+      <x:c r="H58" s="107"/>
+      <x:c r="I58" s="107"/>
+      <x:c r="J58" s="115"/>
+      <x:c r="K58" s="115"/>
+      <x:c r="L58" s="107"/>
+      <x:c r="M58" s="107"/>
+      <x:c r="N58" s="107"/>
+      <x:c r="O58" s="118"/>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="103"/>
+      <x:c r="B59" s="79"/>
+      <x:c r="C59" s="79"/>
+      <x:c r="D59" s="79"/>
+      <x:c r="E59" s="79"/>
+      <x:c r="F59" s="79"/>
+      <x:c r="G59" s="112"/>
+      <x:c r="H59" s="107"/>
+      <x:c r="I59" s="107"/>
+      <x:c r="J59" s="115"/>
+      <x:c r="K59" s="115"/>
+      <x:c r="L59" s="107"/>
+      <x:c r="M59" s="107"/>
+      <x:c r="N59" s="107"/>
+      <x:c r="O59" s="118"/>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="103"/>
+      <x:c r="B60" s="79"/>
+      <x:c r="C60" s="79"/>
+      <x:c r="D60" s="79"/>
+      <x:c r="E60" s="79"/>
+      <x:c r="F60" s="79"/>
+      <x:c r="G60" s="112"/>
+      <x:c r="H60" s="107"/>
+      <x:c r="I60" s="107"/>
+      <x:c r="J60" s="115"/>
+      <x:c r="K60" s="115"/>
+      <x:c r="L60" s="107"/>
+      <x:c r="M60" s="107"/>
+      <x:c r="N60" s="107"/>
+      <x:c r="O60" s="118"/>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="103"/>
+      <x:c r="B61" s="79"/>
+      <x:c r="C61" s="79"/>
+      <x:c r="D61" s="79"/>
+      <x:c r="E61" s="79"/>
+      <x:c r="F61" s="79"/>
+      <x:c r="G61" s="112"/>
+      <x:c r="H61" s="107"/>
+      <x:c r="I61" s="107"/>
+      <x:c r="J61" s="115"/>
+      <x:c r="K61" s="115"/>
+      <x:c r="L61" s="107"/>
+      <x:c r="M61" s="107"/>
+      <x:c r="N61" s="107"/>
+      <x:c r="O61" s="118"/>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="103"/>
+      <x:c r="B62" s="79"/>
+      <x:c r="C62" s="79"/>
+      <x:c r="D62" s="79"/>
+      <x:c r="E62" s="79"/>
+      <x:c r="F62" s="79"/>
+      <x:c r="G62" s="112"/>
+      <x:c r="H62" s="107"/>
+      <x:c r="I62" s="107"/>
+      <x:c r="J62" s="115"/>
+      <x:c r="K62" s="115"/>
+      <x:c r="L62" s="107"/>
+      <x:c r="M62" s="107"/>
+      <x:c r="N62" s="107"/>
+      <x:c r="O62" s="118"/>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="103"/>
+      <x:c r="B63" s="79"/>
+      <x:c r="C63" s="79"/>
+      <x:c r="D63" s="79"/>
+      <x:c r="E63" s="79"/>
+      <x:c r="F63" s="79"/>
+      <x:c r="G63" s="112"/>
+      <x:c r="H63" s="107"/>
+      <x:c r="I63" s="107"/>
+      <x:c r="J63" s="115"/>
+      <x:c r="K63" s="115"/>
+      <x:c r="L63" s="107"/>
+      <x:c r="M63" s="107"/>
+      <x:c r="N63" s="107"/>
+      <x:c r="O63" s="118"/>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="103"/>
+      <x:c r="B64" s="79"/>
+      <x:c r="C64" s="79"/>
+      <x:c r="D64" s="79"/>
+      <x:c r="E64" s="79"/>
+      <x:c r="F64" s="79"/>
+      <x:c r="G64" s="112"/>
+      <x:c r="H64" s="107"/>
+      <x:c r="I64" s="107"/>
+      <x:c r="J64" s="115"/>
+      <x:c r="K64" s="115"/>
+      <x:c r="L64" s="107"/>
+      <x:c r="M64" s="107"/>
+      <x:c r="N64" s="107"/>
+      <x:c r="O64" s="118"/>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="103"/>
+      <x:c r="B65" s="79"/>
+      <x:c r="C65" s="79"/>
+      <x:c r="D65" s="79"/>
+      <x:c r="E65" s="79"/>
+      <x:c r="F65" s="79"/>
+      <x:c r="G65" s="112"/>
+      <x:c r="H65" s="107"/>
+      <x:c r="I65" s="107"/>
+      <x:c r="J65" s="115"/>
+      <x:c r="K65" s="115"/>
+      <x:c r="L65" s="107"/>
+      <x:c r="M65" s="107"/>
+      <x:c r="N65" s="107"/>
+      <x:c r="O65" s="118"/>
+    </x:row>
+    <x:row r="66" ht="22" customHeight="1">
+      <x:c r="A66" s="103"/>
+      <x:c r="B66" s="79"/>
+      <x:c r="C66" s="79"/>
+      <x:c r="D66" s="79"/>
+      <x:c r="E66" s="79"/>
+      <x:c r="F66" s="79"/>
+      <x:c r="G66" s="112"/>
+      <x:c r="H66" s="107"/>
+      <x:c r="I66" s="107"/>
+      <x:c r="J66" s="115"/>
+      <x:c r="K66" s="115"/>
+      <x:c r="L66" s="107"/>
+      <x:c r="M66" s="107"/>
+      <x:c r="N66" s="107"/>
+      <x:c r="O66" s="118"/>
+    </x:row>
+    <x:row r="67" ht="22" customHeight="1">
+      <x:c r="A67" s="103"/>
+      <x:c r="B67" s="79"/>
+      <x:c r="C67" s="79"/>
+      <x:c r="D67" s="79"/>
+      <x:c r="E67" s="79"/>
+      <x:c r="F67" s="79"/>
+      <x:c r="G67" s="112"/>
+      <x:c r="H67" s="107"/>
+      <x:c r="I67" s="107"/>
+      <x:c r="J67" s="115"/>
+      <x:c r="K67" s="115"/>
+      <x:c r="L67" s="107"/>
+      <x:c r="M67" s="107"/>
+      <x:c r="N67" s="107"/>
+      <x:c r="O67" s="118"/>
+    </x:row>
+    <x:row r="68" ht="22" customHeight="1">
+      <x:c r="A68" s="103"/>
+      <x:c r="B68" s="79"/>
+      <x:c r="C68" s="79"/>
+      <x:c r="D68" s="79"/>
+      <x:c r="E68" s="79"/>
+      <x:c r="F68" s="79"/>
+      <x:c r="G68" s="112"/>
+      <x:c r="H68" s="107"/>
+      <x:c r="I68" s="107"/>
+      <x:c r="J68" s="115"/>
+      <x:c r="K68" s="115"/>
+      <x:c r="L68" s="107"/>
+      <x:c r="M68" s="107"/>
+      <x:c r="N68" s="107"/>
+      <x:c r="O68" s="118"/>
+    </x:row>
+    <x:row r="69" ht="22" customHeight="1">
+      <x:c r="A69" s="103"/>
+      <x:c r="B69" s="79"/>
+      <x:c r="C69" s="79"/>
+      <x:c r="D69" s="79"/>
+      <x:c r="E69" s="79"/>
+      <x:c r="F69" s="79"/>
+      <x:c r="G69" s="112"/>
+      <x:c r="H69" s="107"/>
+      <x:c r="I69" s="107"/>
+      <x:c r="J69" s="115"/>
+      <x:c r="K69" s="115"/>
+      <x:c r="L69" s="107"/>
+      <x:c r="M69" s="107"/>
+      <x:c r="N69" s="107"/>
+      <x:c r="O69" s="118"/>
+    </x:row>
+    <x:row r="70" ht="22" customHeight="1">
+      <x:c r="A70" s="103"/>
+      <x:c r="B70" s="79"/>
+      <x:c r="C70" s="79"/>
+      <x:c r="D70" s="79"/>
+      <x:c r="E70" s="79"/>
+      <x:c r="F70" s="79"/>
+      <x:c r="G70" s="112"/>
+      <x:c r="H70" s="107"/>
+      <x:c r="I70" s="107"/>
+      <x:c r="J70" s="115"/>
+      <x:c r="K70" s="115"/>
+      <x:c r="L70" s="107"/>
+      <x:c r="M70" s="107"/>
+      <x:c r="N70" s="107"/>
+      <x:c r="O70" s="118"/>
+    </x:row>
+    <x:row r="71" ht="22" customHeight="1">
+      <x:c r="A71" s="103"/>
+      <x:c r="B71" s="79"/>
+      <x:c r="C71" s="79"/>
+      <x:c r="D71" s="79"/>
+      <x:c r="E71" s="79"/>
+      <x:c r="F71" s="79"/>
+      <x:c r="G71" s="112"/>
+      <x:c r="H71" s="107"/>
+      <x:c r="I71" s="107"/>
+      <x:c r="J71" s="115"/>
+      <x:c r="K71" s="115"/>
+      <x:c r="L71" s="107"/>
+      <x:c r="M71" s="107"/>
+      <x:c r="N71" s="107"/>
+      <x:c r="O71" s="118"/>
+    </x:row>
+    <x:row r="72" ht="22" customHeight="1">
+      <x:c r="A72" s="103"/>
+      <x:c r="B72" s="79"/>
+      <x:c r="C72" s="79"/>
+      <x:c r="D72" s="79"/>
+      <x:c r="E72" s="79"/>
+      <x:c r="F72" s="79"/>
+      <x:c r="G72" s="112"/>
+      <x:c r="H72" s="107"/>
+      <x:c r="I72" s="107"/>
+      <x:c r="J72" s="115"/>
+      <x:c r="K72" s="115"/>
+      <x:c r="L72" s="107"/>
+      <x:c r="M72" s="107"/>
+      <x:c r="N72" s="107"/>
+      <x:c r="O72" s="118"/>
+    </x:row>
+    <x:row r="73" ht="22" customHeight="1">
+      <x:c r="A73" s="103"/>
+      <x:c r="B73" s="79"/>
+      <x:c r="C73" s="79"/>
+      <x:c r="D73" s="79"/>
+      <x:c r="E73" s="79"/>
+      <x:c r="F73" s="79"/>
+      <x:c r="G73" s="112"/>
+      <x:c r="H73" s="107"/>
+      <x:c r="I73" s="107"/>
+      <x:c r="J73" s="115"/>
+      <x:c r="K73" s="115"/>
+      <x:c r="L73" s="107"/>
+      <x:c r="M73" s="107"/>
+      <x:c r="N73" s="107"/>
+      <x:c r="O73" s="118"/>
+    </x:row>
+    <x:row r="74" ht="22" customHeight="1">
+      <x:c r="A74" s="103"/>
+      <x:c r="B74" s="79"/>
+      <x:c r="C74" s="79"/>
+      <x:c r="D74" s="79"/>
+      <x:c r="E74" s="79"/>
+      <x:c r="F74" s="79"/>
+      <x:c r="G74" s="112"/>
+      <x:c r="H74" s="107"/>
+      <x:c r="I74" s="107"/>
+      <x:c r="J74" s="115"/>
+      <x:c r="K74" s="115"/>
+      <x:c r="L74" s="107"/>
+      <x:c r="M74" s="107"/>
+      <x:c r="N74" s="107"/>
+      <x:c r="O74" s="118"/>
+    </x:row>
+    <x:row r="75" ht="22" customHeight="1">
+      <x:c r="A75" s="103"/>
+      <x:c r="B75" s="79"/>
+      <x:c r="C75" s="79"/>
+      <x:c r="D75" s="79"/>
+      <x:c r="E75" s="79"/>
+      <x:c r="F75" s="79"/>
+      <x:c r="G75" s="112"/>
+      <x:c r="H75" s="107"/>
+      <x:c r="I75" s="107"/>
+      <x:c r="J75" s="115"/>
+      <x:c r="K75" s="115"/>
+      <x:c r="L75" s="107"/>
+      <x:c r="M75" s="107"/>
+      <x:c r="N75" s="107"/>
+      <x:c r="O75" s="118"/>
+    </x:row>
+    <x:row r="76" ht="22" customHeight="1">
+      <x:c r="A76" s="103"/>
+      <x:c r="B76" s="79"/>
+      <x:c r="C76" s="79"/>
+      <x:c r="D76" s="79"/>
+      <x:c r="E76" s="79"/>
+      <x:c r="F76" s="79"/>
+      <x:c r="G76" s="112"/>
+      <x:c r="H76" s="107"/>
+      <x:c r="I76" s="107"/>
+      <x:c r="J76" s="115"/>
+      <x:c r="K76" s="115"/>
+      <x:c r="L76" s="107"/>
+      <x:c r="M76" s="107"/>
+      <x:c r="N76" s="107"/>
+      <x:c r="O76" s="118"/>
+    </x:row>
+    <x:row r="77" ht="22" customHeight="1">
+      <x:c r="A77" s="103"/>
+      <x:c r="B77" s="79"/>
+      <x:c r="C77" s="79"/>
+      <x:c r="D77" s="79"/>
+      <x:c r="E77" s="79"/>
+      <x:c r="F77" s="79"/>
+      <x:c r="G77" s="112"/>
+      <x:c r="H77" s="107"/>
+      <x:c r="I77" s="107"/>
+      <x:c r="J77" s="115"/>
+      <x:c r="K77" s="115"/>
+      <x:c r="L77" s="107"/>
+      <x:c r="M77" s="107"/>
+      <x:c r="N77" s="107"/>
+      <x:c r="O77" s="118"/>
+    </x:row>
+    <x:row r="78" ht="22" customHeight="1">
+      <x:c r="A78" s="103"/>
+      <x:c r="B78" s="79"/>
+      <x:c r="C78" s="79"/>
+      <x:c r="D78" s="79"/>
+      <x:c r="E78" s="79"/>
+      <x:c r="F78" s="79"/>
+      <x:c r="G78" s="112"/>
+      <x:c r="H78" s="107"/>
+      <x:c r="I78" s="107"/>
+      <x:c r="J78" s="115"/>
+      <x:c r="K78" s="115"/>
+      <x:c r="L78" s="107"/>
+      <x:c r="M78" s="107"/>
+      <x:c r="N78" s="107"/>
+      <x:c r="O78" s="118"/>
+    </x:row>
+    <x:row r="79" ht="22" customHeight="1">
+      <x:c r="A79" s="103"/>
+      <x:c r="B79" s="79"/>
+      <x:c r="C79" s="79"/>
+      <x:c r="D79" s="79"/>
+      <x:c r="E79" s="79"/>
+      <x:c r="F79" s="79"/>
+      <x:c r="G79" s="112"/>
+      <x:c r="H79" s="107"/>
+      <x:c r="I79" s="107"/>
+      <x:c r="J79" s="115"/>
+      <x:c r="K79" s="115"/>
+      <x:c r="L79" s="107"/>
+      <x:c r="M79" s="107"/>
+      <x:c r="N79" s="107"/>
+      <x:c r="O79" s="118"/>
+    </x:row>
+    <x:row r="80" ht="22" customHeight="1">
+      <x:c r="A80" s="103"/>
+      <x:c r="B80" s="79"/>
+      <x:c r="C80" s="79"/>
+      <x:c r="D80" s="79"/>
+      <x:c r="E80" s="79"/>
+      <x:c r="F80" s="79"/>
+      <x:c r="G80" s="112"/>
+      <x:c r="H80" s="107"/>
+      <x:c r="I80" s="107"/>
+      <x:c r="J80" s="115"/>
+      <x:c r="K80" s="115"/>
+      <x:c r="L80" s="107"/>
+      <x:c r="M80" s="107"/>
+      <x:c r="N80" s="107"/>
+      <x:c r="O80" s="118"/>
+    </x:row>
+    <x:row r="81" ht="22" customHeight="1">
+      <x:c r="A81" s="103"/>
+      <x:c r="B81" s="79"/>
+      <x:c r="C81" s="79"/>
+      <x:c r="D81" s="79"/>
+      <x:c r="E81" s="79"/>
+      <x:c r="F81" s="79"/>
+      <x:c r="G81" s="112"/>
+      <x:c r="H81" s="107"/>
+      <x:c r="I81" s="107"/>
+      <x:c r="J81" s="115"/>
+      <x:c r="K81" s="115"/>
+      <x:c r="L81" s="107"/>
+      <x:c r="M81" s="107"/>
+      <x:c r="N81" s="107"/>
+      <x:c r="O81" s="118"/>
+    </x:row>
+    <x:row r="82" ht="22" customHeight="1">
+      <x:c r="A82" s="103"/>
+      <x:c r="B82" s="79"/>
+      <x:c r="C82" s="79"/>
+      <x:c r="D82" s="79"/>
+      <x:c r="E82" s="79"/>
+      <x:c r="F82" s="79"/>
+      <x:c r="G82" s="112"/>
+      <x:c r="H82" s="107"/>
+      <x:c r="I82" s="107"/>
+      <x:c r="J82" s="115"/>
+      <x:c r="K82" s="115"/>
+      <x:c r="L82" s="107"/>
+      <x:c r="M82" s="107"/>
+      <x:c r="N82" s="107"/>
+      <x:c r="O82" s="118"/>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="103"/>
+      <x:c r="B83" s="79"/>
+      <x:c r="C83" s="79"/>
+      <x:c r="D83" s="79"/>
+      <x:c r="E83" s="79"/>
+      <x:c r="F83" s="79"/>
+      <x:c r="G83" s="112"/>
+      <x:c r="H83" s="107"/>
+      <x:c r="I83" s="107"/>
+      <x:c r="J83" s="115"/>
+      <x:c r="K83" s="115"/>
+      <x:c r="L83" s="107"/>
+      <x:c r="M83" s="107"/>
+      <x:c r="N83" s="107"/>
+      <x:c r="O83" s="118"/>
+    </x:row>
+    <x:row r="84" ht="22" customHeight="1">
+      <x:c r="A84" s="103"/>
+      <x:c r="B84" s="79"/>
+      <x:c r="C84" s="79"/>
+      <x:c r="D84" s="79"/>
+      <x:c r="E84" s="79"/>
+      <x:c r="F84" s="79"/>
+      <x:c r="G84" s="112"/>
+      <x:c r="H84" s="107"/>
+      <x:c r="I84" s="107"/>
+      <x:c r="J84" s="115"/>
+      <x:c r="K84" s="115"/>
+      <x:c r="L84" s="107"/>
+      <x:c r="M84" s="107"/>
+      <x:c r="N84" s="107"/>
+      <x:c r="O84" s="118"/>
+    </x:row>
+    <x:row r="85" ht="22" customHeight="1">
+      <x:c r="A85" s="103"/>
+      <x:c r="B85" s="79"/>
+      <x:c r="C85" s="79"/>
+      <x:c r="D85" s="79"/>
+      <x:c r="E85" s="79"/>
+      <x:c r="F85" s="79"/>
+      <x:c r="G85" s="112"/>
+      <x:c r="H85" s="107"/>
+      <x:c r="I85" s="107"/>
+      <x:c r="J85" s="115"/>
+      <x:c r="K85" s="115"/>
+      <x:c r="L85" s="107"/>
+      <x:c r="M85" s="107"/>
+      <x:c r="N85" s="107"/>
+      <x:c r="O85" s="118"/>
+    </x:row>
+    <x:row r="86" ht="22" customHeight="1">
+      <x:c r="A86" s="103"/>
+      <x:c r="B86" s="79"/>
+      <x:c r="C86" s="79"/>
+      <x:c r="D86" s="79"/>
+      <x:c r="E86" s="79"/>
+      <x:c r="F86" s="79"/>
+      <x:c r="G86" s="112"/>
+      <x:c r="H86" s="107"/>
+      <x:c r="I86" s="107"/>
+      <x:c r="J86" s="115"/>
+      <x:c r="K86" s="115"/>
+      <x:c r="L86" s="107"/>
+      <x:c r="M86" s="107"/>
+      <x:c r="N86" s="107"/>
+      <x:c r="O86" s="118"/>
+    </x:row>
+    <x:row r="87" ht="22" customHeight="1">
+      <x:c r="A87" s="103"/>
+      <x:c r="B87" s="79"/>
+      <x:c r="C87" s="79"/>
+      <x:c r="D87" s="79"/>
+      <x:c r="E87" s="79"/>
+      <x:c r="F87" s="79"/>
+      <x:c r="G87" s="112"/>
+      <x:c r="H87" s="107"/>
+      <x:c r="I87" s="107"/>
+      <x:c r="J87" s="115"/>
+      <x:c r="K87" s="115"/>
+      <x:c r="L87" s="107"/>
+      <x:c r="M87" s="107"/>
+      <x:c r="N87" s="107"/>
+      <x:c r="O87" s="118"/>
+    </x:row>
+    <x:row r="88" ht="22" customHeight="1">
+      <x:c r="A88" s="103"/>
+      <x:c r="B88" s="79"/>
+      <x:c r="C88" s="79"/>
+      <x:c r="D88" s="79"/>
+      <x:c r="E88" s="79"/>
+      <x:c r="F88" s="79"/>
+      <x:c r="G88" s="112"/>
+      <x:c r="H88" s="107"/>
+      <x:c r="I88" s="107"/>
+      <x:c r="J88" s="115"/>
+      <x:c r="K88" s="115"/>
+      <x:c r="L88" s="107"/>
+      <x:c r="M88" s="107"/>
+      <x:c r="N88" s="107"/>
+      <x:c r="O88" s="118"/>
+    </x:row>
+    <x:row r="89" ht="22" customHeight="1">
+      <x:c r="A89" s="103"/>
+      <x:c r="B89" s="79"/>
+      <x:c r="C89" s="79"/>
+      <x:c r="D89" s="79"/>
+      <x:c r="E89" s="79"/>
+      <x:c r="F89" s="79"/>
+      <x:c r="G89" s="112"/>
+      <x:c r="H89" s="107"/>
+      <x:c r="I89" s="107"/>
+      <x:c r="J89" s="115"/>
+      <x:c r="K89" s="115"/>
+      <x:c r="L89" s="107"/>
+      <x:c r="M89" s="107"/>
+      <x:c r="N89" s="107"/>
+      <x:c r="O89" s="118"/>
+    </x:row>
+    <x:row r="90" ht="22" customHeight="1">
+      <x:c r="A90" s="103"/>
+      <x:c r="B90" s="79"/>
+      <x:c r="C90" s="79"/>
+      <x:c r="D90" s="79"/>
+      <x:c r="E90" s="79"/>
+      <x:c r="F90" s="79"/>
+      <x:c r="G90" s="112"/>
+      <x:c r="H90" s="107"/>
+      <x:c r="I90" s="107"/>
+      <x:c r="J90" s="115"/>
+      <x:c r="K90" s="115"/>
+      <x:c r="L90" s="107"/>
+      <x:c r="M90" s="107"/>
+      <x:c r="N90" s="107"/>
+      <x:c r="O90" s="118"/>
+    </x:row>
+    <x:row r="91" ht="22" customHeight="1">
+      <x:c r="A91" s="103"/>
+      <x:c r="B91" s="79"/>
+      <x:c r="C91" s="79"/>
+      <x:c r="D91" s="79"/>
+      <x:c r="E91" s="79"/>
+      <x:c r="F91" s="79"/>
+      <x:c r="G91" s="112"/>
+      <x:c r="H91" s="107"/>
+      <x:c r="I91" s="107"/>
+      <x:c r="J91" s="115"/>
+      <x:c r="K91" s="115"/>
+      <x:c r="L91" s="107"/>
+      <x:c r="M91" s="107"/>
+      <x:c r="N91" s="107"/>
+      <x:c r="O91" s="118"/>
+    </x:row>
+    <x:row r="92" ht="22" customHeight="1">
+      <x:c r="A92" s="103"/>
+      <x:c r="B92" s="79"/>
+      <x:c r="C92" s="79"/>
+      <x:c r="D92" s="79"/>
+      <x:c r="E92" s="79"/>
+      <x:c r="F92" s="79"/>
+      <x:c r="G92" s="112"/>
+      <x:c r="H92" s="107"/>
+      <x:c r="I92" s="107"/>
+      <x:c r="J92" s="115"/>
+      <x:c r="K92" s="115"/>
+      <x:c r="L92" s="107"/>
+      <x:c r="M92" s="107"/>
+      <x:c r="N92" s="107"/>
+      <x:c r="O92" s="118"/>
+    </x:row>
+    <x:row r="93" ht="22" customHeight="1">
+      <x:c r="A93" s="103"/>
+      <x:c r="B93" s="79"/>
+      <x:c r="C93" s="79"/>
+      <x:c r="D93" s="79"/>
+      <x:c r="E93" s="79"/>
+      <x:c r="F93" s="79"/>
+      <x:c r="G93" s="112"/>
+      <x:c r="H93" s="107"/>
+      <x:c r="I93" s="107"/>
+      <x:c r="J93" s="115"/>
+      <x:c r="K93" s="115"/>
+      <x:c r="L93" s="107"/>
+      <x:c r="M93" s="107"/>
+      <x:c r="N93" s="107"/>
+      <x:c r="O93" s="118"/>
+    </x:row>
+    <x:row r="94" ht="22" customHeight="1">
+      <x:c r="A94" s="103"/>
+      <x:c r="B94" s="79"/>
+      <x:c r="C94" s="79"/>
+      <x:c r="D94" s="79"/>
+      <x:c r="E94" s="79"/>
+      <x:c r="F94" s="79"/>
+      <x:c r="G94" s="112"/>
+      <x:c r="H94" s="107"/>
+      <x:c r="I94" s="107"/>
+      <x:c r="J94" s="115"/>
+      <x:c r="K94" s="115"/>
+      <x:c r="L94" s="107"/>
+      <x:c r="M94" s="107"/>
+      <x:c r="N94" s="107"/>
+      <x:c r="O94" s="118"/>
+    </x:row>
+    <x:row r="95" ht="22" customHeight="1">
+      <x:c r="A95" s="103"/>
+      <x:c r="B95" s="79"/>
+      <x:c r="C95" s="79"/>
+      <x:c r="D95" s="79"/>
+      <x:c r="E95" s="79"/>
+      <x:c r="F95" s="79"/>
+      <x:c r="G95" s="112"/>
+      <x:c r="H95" s="107"/>
+      <x:c r="I95" s="107"/>
+      <x:c r="J95" s="115"/>
+      <x:c r="K95" s="115"/>
+      <x:c r="L95" s="107"/>
+      <x:c r="M95" s="107"/>
+      <x:c r="N95" s="107"/>
+      <x:c r="O95" s="118"/>
+    </x:row>
+    <x:row r="96" ht="22" customHeight="1">
+      <x:c r="A96" s="103"/>
+      <x:c r="B96" s="79"/>
+      <x:c r="C96" s="79"/>
+      <x:c r="D96" s="79"/>
+      <x:c r="E96" s="79"/>
+      <x:c r="F96" s="79"/>
+      <x:c r="G96" s="112"/>
+      <x:c r="H96" s="107"/>
+      <x:c r="I96" s="107"/>
+      <x:c r="J96" s="115"/>
+      <x:c r="K96" s="115"/>
+      <x:c r="L96" s="107"/>
+      <x:c r="M96" s="107"/>
+      <x:c r="N96" s="107"/>
+      <x:c r="O96" s="118"/>
+    </x:row>
+    <x:row r="97" ht="22" customHeight="1">
+      <x:c r="A97" s="103"/>
+      <x:c r="B97" s="79"/>
+      <x:c r="C97" s="79"/>
+      <x:c r="D97" s="79"/>
+      <x:c r="E97" s="79"/>
+      <x:c r="F97" s="79"/>
+      <x:c r="G97" s="112"/>
+      <x:c r="H97" s="107"/>
+      <x:c r="I97" s="107"/>
+      <x:c r="J97" s="115"/>
+      <x:c r="K97" s="115"/>
+      <x:c r="L97" s="107"/>
+      <x:c r="M97" s="107"/>
+      <x:c r="N97" s="107"/>
+      <x:c r="O97" s="118"/>
+    </x:row>
+    <x:row r="98" ht="22" customHeight="1">
+      <x:c r="A98" s="103"/>
+      <x:c r="B98" s="79"/>
+      <x:c r="C98" s="79"/>
+      <x:c r="D98" s="79"/>
+      <x:c r="E98" s="79"/>
+      <x:c r="F98" s="79"/>
+      <x:c r="G98" s="112"/>
+      <x:c r="H98" s="107"/>
+      <x:c r="I98" s="107"/>
+      <x:c r="J98" s="115"/>
+      <x:c r="K98" s="115"/>
+      <x:c r="L98" s="107"/>
+      <x:c r="M98" s="107"/>
+      <x:c r="N98" s="107"/>
+      <x:c r="O98" s="118"/>
+    </x:row>
+    <x:row r="99" ht="22" customHeight="1">
+      <x:c r="A99" s="103"/>
+      <x:c r="B99" s="79"/>
+      <x:c r="C99" s="79"/>
+      <x:c r="D99" s="79"/>
+      <x:c r="E99" s="79"/>
+      <x:c r="F99" s="79"/>
+      <x:c r="G99" s="112"/>
+      <x:c r="H99" s="107"/>
+      <x:c r="I99" s="107"/>
+      <x:c r="J99" s="115"/>
+      <x:c r="K99" s="115"/>
+      <x:c r="L99" s="107"/>
+      <x:c r="M99" s="107"/>
+      <x:c r="N99" s="107"/>
+      <x:c r="O99" s="118"/>
+    </x:row>
+    <x:row r="100" ht="22" customHeight="1">
+      <x:c r="A100" s="103"/>
+      <x:c r="B100" s="79"/>
+      <x:c r="C100" s="79"/>
+      <x:c r="D100" s="79"/>
+      <x:c r="E100" s="79"/>
+      <x:c r="F100" s="79"/>
+      <x:c r="G100" s="112"/>
+      <x:c r="H100" s="107"/>
+      <x:c r="I100" s="107"/>
+      <x:c r="J100" s="115"/>
+      <x:c r="K100" s="115"/>
+      <x:c r="L100" s="107"/>
+      <x:c r="M100" s="107"/>
+      <x:c r="N100" s="107"/>
+      <x:c r="O100" s="118"/>
+    </x:row>
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="103"/>
+      <x:c r="B101" s="79"/>
+      <x:c r="C101" s="79"/>
+      <x:c r="D101" s="79"/>
+      <x:c r="E101" s="79"/>
+      <x:c r="F101" s="79"/>
+      <x:c r="G101" s="112"/>
+      <x:c r="H101" s="107"/>
+      <x:c r="I101" s="107"/>
+      <x:c r="J101" s="115"/>
+      <x:c r="K101" s="115"/>
+      <x:c r="L101" s="107"/>
+      <x:c r="M101" s="107"/>
+      <x:c r="N101" s="107"/>
+      <x:c r="O101" s="118"/>
+    </x:row>
+    <x:row r="102" ht="22" customHeight="1">
+      <x:c r="A102" s="103"/>
+      <x:c r="B102" s="79"/>
+      <x:c r="C102" s="79"/>
+      <x:c r="D102" s="79"/>
+      <x:c r="E102" s="79"/>
+      <x:c r="F102" s="79"/>
+      <x:c r="G102" s="112"/>
+      <x:c r="H102" s="107"/>
+      <x:c r="I102" s="107"/>
+      <x:c r="J102" s="115"/>
+      <x:c r="K102" s="115"/>
+      <x:c r="L102" s="107"/>
+      <x:c r="M102" s="107"/>
+      <x:c r="N102" s="107"/>
+      <x:c r="O102" s="118"/>
+    </x:row>
+    <x:row r="103" ht="22" customHeight="1">
+      <x:c r="A103" s="103"/>
+      <x:c r="B103" s="79"/>
+      <x:c r="C103" s="79"/>
+      <x:c r="D103" s="79"/>
+      <x:c r="E103" s="79"/>
+      <x:c r="F103" s="79"/>
+      <x:c r="G103" s="112"/>
+      <x:c r="H103" s="107"/>
+      <x:c r="I103" s="107"/>
+      <x:c r="J103" s="115"/>
+      <x:c r="K103" s="115"/>
+      <x:c r="L103" s="107"/>
+      <x:c r="M103" s="107"/>
+      <x:c r="N103" s="107"/>
+      <x:c r="O103" s="118"/>
+    </x:row>
+    <x:row r="104" ht="22" customHeight="1">
+      <x:c r="A104" s="104"/>
+      <x:c r="B104" s="82"/>
+      <x:c r="C104" s="82"/>
+      <x:c r="D104" s="82"/>
+      <x:c r="E104" s="82"/>
+      <x:c r="F104" s="82"/>
+      <x:c r="G104" s="113"/>
+      <x:c r="H104" s="109"/>
+      <x:c r="I104" s="109"/>
+      <x:c r="J104" s="116"/>
+      <x:c r="K104" s="116"/>
+      <x:c r="L104" s="109"/>
+      <x:c r="M104" s="109"/>
+      <x:c r="N104" s="109"/>
+      <x:c r="O104" s="119"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A3:O3"/>
+  </x:mergeCells>
+  <x:dataValidations count="4">
+    <x:dataValidation type="list" sqref="C6:C104">
+      <x:formula1>"YES,NO"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D6:D104">
+      <x:formula1>'模板库'!$A$5:$A$104</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E6:E104">
+      <x:formula1>"1,2"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="F6:F104">
+      <x:formula1>1</x:formula1>
+      <x:formula2>7</x:formula2>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FFA5A5A5"/>
@@ -2234,8 +4120,8 @@
     <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="68" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="72" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2245,6 +4131,9 @@
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
@@ -2255,6 +4144,9 @@
       <x:c r="D2" s="2"/>
       <x:c r="E2" s="2"/>
       <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+      <x:c r="I2" s="2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2"/>
@@ -2263,6 +4155,9 @@
       <x:c r="D3" s="2"/>
       <x:c r="E3" s="2"/>
       <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+      <x:c r="H3" s="2"/>
+      <x:c r="I3" s="2"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="8" t="str">
@@ -2273,10 +4168,11 @@
       <x:c r="D4" s="2"/>
       <x:c r="E4" s="2"/>
       <x:c r="F4" s="2"/>
-      <x:c r="H4" s="127" t="str">
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="20" t="str">
         <x:v>UI key</x:v>
       </x:c>
-      <x:c r="I4" s="127" t="str">
+      <x:c r="I4" s="20" t="str">
         <x:v>界面文本（请勿修改）</x:v>
       </x:c>
     </x:row>
@@ -2287,10 +4183,11 @@
       <x:c r="D5" s="2"/>
       <x:c r="E5" s="2"/>
       <x:c r="F5" s="2"/>
-      <x:c r="H5" s="128" t="str">
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="138" t="str">
         <x:v>button.load</x:v>
       </x:c>
-      <x:c r="I5" s="128" t="str">
+      <x:c r="I5" s="138" t="str">
         <x:v>载入模板</x:v>
       </x:c>
     </x:row>
@@ -2298,17 +4195,18 @@
       <x:c r="A6" s="12" t="str">
         <x:v>自动发送</x:v>
       </x:c>
-      <x:c r="B6" s="110" t="b">
+      <x:c r="B6" s="124" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
       <x:c r="D6" s="2"/>
       <x:c r="E6" s="2"/>
       <x:c r="F6" s="2"/>
-      <x:c r="H6" s="128" t="str">
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="138" t="str">
         <x:v>button.preview</x:v>
       </x:c>
-      <x:c r="I6" s="128" t="str">
+      <x:c r="I6" s="138" t="str">
         <x:v>更新预览</x:v>
       </x:c>
     </x:row>
@@ -2316,17 +4214,18 @@
       <x:c r="A7" s="12" t="str">
         <x:v>Outlook 类型</x:v>
       </x:c>
-      <x:c r="B7" s="111" t="str">
+      <x:c r="B7" s="125" t="str">
         <x:v>经典版 Outlook</x:v>
       </x:c>
       <x:c r="C7" s="2"/>
       <x:c r="D7" s="2"/>
       <x:c r="E7" s="2"/>
       <x:c r="F7" s="2"/>
-      <x:c r="H7" s="128" t="str">
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="138" t="str">
         <x:v>button.generate</x:v>
       </x:c>
-      <x:c r="I7" s="128" t="str">
+      <x:c r="I7" s="138" t="str">
         <x:v>生成邮件</x:v>
       </x:c>
     </x:row>
@@ -2334,300 +4233,324 @@
       <x:c r="A8" s="12" t="str">
         <x:v>batch_date 示例</x:v>
       </x:c>
-      <x:c r="B8" s="112" t="n">
+      <x:c r="B8" s="126" t="n">
         <x:f>TODAY()-1</x:f>
-        <x:v>46280</x:v>
+        <x:v>46281</x:v>
       </x:c>
       <x:c r="C8" s="2"/>
       <x:c r="D8" s="2"/>
       <x:c r="E8" s="2"/>
       <x:c r="F8" s="2"/>
-      <x:c r="H8" s="128" t="str">
-        <x:v>checkbox.autosend</x:v>
-      </x:c>
-      <x:c r="I8" s="128" t="str">
-        <x:v>确认后自动发送</x:v>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="138" t="str">
+        <x:v>button.task.load</x:v>
+      </x:c>
+      <x:c r="I8" s="138" t="str">
+        <x:v>加载选中任务</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="12" t="str">
         <x:v>日期格式</x:v>
       </x:c>
-      <x:c r="B9" s="111" t="str">
+      <x:c r="B9" s="125" t="str">
         <x:v>yyyy-mm-dd</x:v>
       </x:c>
       <x:c r="C9" s="2"/>
       <x:c r="D9" s="2"/>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
-      <x:c r="H9" s="128" t="str">
-        <x:v>status.initialized</x:v>
-      </x:c>
-      <x:c r="I9" s="128" t="str">
-        <x:v>初始化完成。填写黄色单元格后生成邮件。</x:v>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="138" t="str">
+        <x:v>button.task.save</x:v>
+      </x:c>
+      <x:c r="I9" s="138" t="str">
+        <x:v>保存并启用</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="2"/>
-      <x:c r="B10" s="2"/>
+      <x:c r="A10" s="12" t="str">
+        <x:v>参数滚动位置</x:v>
+      </x:c>
+      <x:c r="B10" s="125" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
-      <x:c r="H10" s="128" t="str">
-        <x:v>status.preview</x:v>
-      </x:c>
-      <x:c r="I10" s="128" t="str">
-        <x:v>预览已更新。</x:v>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="138" t="str">
+        <x:v>button.task.pause</x:v>
+      </x:c>
+      <x:c r="I10" s="138" t="str">
+        <x:v>暂停任务</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="8" t="str">
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="138" t="str">
+        <x:v>button.task.refresh</x:v>
+      </x:c>
+      <x:c r="I11" s="138" t="str">
+        <x:v>刷新计划</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="8" t="str">
         <x:v>首次安装</x:v>
       </x:c>
-      <x:c r="B11" s="10"/>
-      <x:c r="C11" s="10"/>
-      <x:c r="D11" s="10"/>
-      <x:c r="E11" s="10"/>
-      <x:c r="F11" s="9"/>
-      <x:c r="H11" s="128" t="str">
-        <x:v>status.missing</x:v>
-      </x:c>
-      <x:c r="I11" s="128" t="str">
-        <x:v>请填写变量：</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="56" t="str">
+      <x:c r="B12" s="10"/>
+      <x:c r="C12" s="10"/>
+      <x:c r="D12" s="10"/>
+      <x:c r="E12" s="10"/>
+      <x:c r="F12" s="9"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="138" t="str">
+        <x:v>button.task.test</x:v>
+      </x:c>
+      <x:c r="I12" s="138" t="str">
+        <x:v>测试并打开邮件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="51" t="str">
         <x:v>1. 将本文件另存为“Excel 启用宏的工作簿 (*.xlsm)”。
 2. 按 Alt+F11，选择“文件 → 导入文件”，导入 vba\modOutlookTemplateTool.bas。
 3. 回到 Excel，按 Alt+F8 运行 SetupWorkbook；保存并重新打开工作簿。
-4. 若公司禁用未签名宏，请让 IT 将工作簿放入受信任位置或使用公司证书签名。</x:v>
-      </x:c>
-      <x:c r="B12" s="57"/>
-      <x:c r="C12" s="57"/>
-      <x:c r="D12" s="57"/>
-      <x:c r="E12" s="57"/>
-      <x:c r="F12" s="58"/>
-      <x:c r="H12" s="128" t="str">
+4. 定时任务依赖 Excel 常驻打开。若公司禁用未签名宏，请由 IT 使用受信任位置或公司证书。</x:v>
+      </x:c>
+      <x:c r="B13" s="52"/>
+      <x:c r="C13" s="52"/>
+      <x:c r="D13" s="52"/>
+      <x:c r="E13" s="52"/>
+      <x:c r="F13" s="53"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="138" t="str">
+        <x:v>checkbox.autosend</x:v>
+      </x:c>
+      <x:c r="I13" s="138" t="str">
+        <x:v>确认后自动发送</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="54"/>
+      <x:c r="B14" s="55"/>
+      <x:c r="C14" s="55"/>
+      <x:c r="D14" s="55"/>
+      <x:c r="E14" s="55"/>
+      <x:c r="F14" s="56"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="138" t="str">
+        <x:v>status.initialized</x:v>
+      </x:c>
+      <x:c r="I14" s="138" t="str">
+        <x:v>初始化完成。填写黄色单元格后生成邮件。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="54"/>
+      <x:c r="B15" s="55"/>
+      <x:c r="C15" s="55"/>
+      <x:c r="D15" s="55"/>
+      <x:c r="E15" s="55"/>
+      <x:c r="F15" s="56"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="138" t="str">
+        <x:v>status.preview</x:v>
+      </x:c>
+      <x:c r="I15" s="138" t="str">
+        <x:v>预览已更新。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="54"/>
+      <x:c r="B16" s="55"/>
+      <x:c r="C16" s="55"/>
+      <x:c r="D16" s="55"/>
+      <x:c r="E16" s="55"/>
+      <x:c r="F16" s="56"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="138" t="str">
+        <x:v>status.missing</x:v>
+      </x:c>
+      <x:c r="I16" s="138" t="str">
+        <x:v>请填写变量：</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="54"/>
+      <x:c r="B17" s="55"/>
+      <x:c r="C17" s="55"/>
+      <x:c r="D17" s="55"/>
+      <x:c r="E17" s="55"/>
+      <x:c r="F17" s="56"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="138" t="str">
+        <x:v>status.no.parameters</x:v>
+      </x:c>
+      <x:c r="I17" s="138" t="str">
+        <x:v>当前模板没有参数。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="57"/>
+      <x:c r="B18" s="58"/>
+      <x:c r="C18" s="58"/>
+      <x:c r="D18" s="58"/>
+      <x:c r="E18" s="58"/>
+      <x:c r="F18" s="59"/>
+      <x:c r="G18" s="2"/>
+      <x:c r="H18" s="138" t="str">
         <x:v>status.cancelled</x:v>
       </x:c>
-      <x:c r="I12" s="128" t="str">
+      <x:c r="I18" s="138" t="str">
         <x:v>已取消发送。</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="59"/>
-      <x:c r="B13" s="60"/>
-      <x:c r="C13" s="60"/>
-      <x:c r="D13" s="60"/>
-      <x:c r="E13" s="60"/>
-      <x:c r="F13" s="61"/>
-      <x:c r="H13" s="128" t="str">
+    <x:row r="19">
+      <x:c r="A19" s="2"/>
+      <x:c r="B19" s="2"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="138" t="str">
         <x:v>status.sent</x:v>
       </x:c>
-      <x:c r="I13" s="128" t="str">
+      <x:c r="I19" s="138" t="str">
         <x:v>邮件已交给 Outlook 发送。请在“已发送邮件”中核对。</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="59"/>
-      <x:c r="B14" s="60"/>
-      <x:c r="C14" s="60"/>
-      <x:c r="D14" s="60"/>
-      <x:c r="E14" s="60"/>
-      <x:c r="F14" s="61"/>
-      <x:c r="H14" s="128" t="str">
+    <x:row r="20">
+      <x:c r="A20" s="8" t="str">
+        <x:v>兼容性与定时限制</x:v>
+      </x:c>
+      <x:c r="B20" s="10"/>
+      <x:c r="C20" s="10"/>
+      <x:c r="D20" s="10"/>
+      <x:c r="E20" s="10"/>
+      <x:c r="F20" s="9"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="138" t="str">
         <x:v>status.opened</x:v>
       </x:c>
-      <x:c r="I14" s="128" t="str">
+      <x:c r="I20" s="138" t="str">
         <x:v>已打开可编辑邮件窗口。请检查后在 Outlook 中发送。</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="22" customHeight="1">
-      <x:c r="A15" s="59"/>
-      <x:c r="B15" s="60"/>
-      <x:c r="C15" s="60"/>
-      <x:c r="D15" s="60"/>
-      <x:c r="E15" s="60"/>
-      <x:c r="F15" s="61"/>
-      <x:c r="H15" s="128" t="str">
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="130" t="str">
+        <x:v>工具通过 Excel VBA 调用经典 Outlook 自带的 COM 对象，不需要再次登录，也不使用任务计划程序、PowerShell、Java、第三方 DLL 或自定义 EXE。循环任务使用 Application.OnTime：Excel 必须保持打开，Windows 用户必须登录，电脑不能休眠。计划时间已经过去时只记录“已错过”，不会补发。</x:v>
+      </x:c>
+      <x:c r="B21" s="131"/>
+      <x:c r="C21" s="131"/>
+      <x:c r="D21" s="131"/>
+      <x:c r="E21" s="131"/>
+      <x:c r="F21" s="132"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="138" t="str">
         <x:v>status.autosend.on</x:v>
       </x:c>
-      <x:c r="I15" s="128" t="str">
+      <x:c r="I21" s="138" t="str">
         <x:v>自动发送已启用；点击“生成邮件”后仍会先要求确认。</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="59"/>
-      <x:c r="B16" s="60"/>
-      <x:c r="C16" s="60"/>
-      <x:c r="D16" s="60"/>
-      <x:c r="E16" s="60"/>
-      <x:c r="F16" s="61"/>
-      <x:c r="H16" s="128" t="str">
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="133"/>
+      <x:c r="B22" s="129"/>
+      <x:c r="C22" s="129"/>
+      <x:c r="D22" s="129"/>
+      <x:c r="E22" s="129"/>
+      <x:c r="F22" s="134"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="138" t="str">
         <x:v>status.autosend.off</x:v>
       </x:c>
-      <x:c r="I16" s="128" t="str">
+      <x:c r="I22" s="138" t="str">
         <x:v>自动发送未启用；点击“生成邮件”将打开可编辑邮件窗口。</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="22" customHeight="1">
-      <x:c r="A17" s="62"/>
-      <x:c r="B17" s="63"/>
-      <x:c r="C17" s="63"/>
-      <x:c r="D17" s="63"/>
-      <x:c r="E17" s="63"/>
-      <x:c r="F17" s="64"/>
-      <x:c r="H17" s="128" t="str">
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="133"/>
+      <x:c r="B23" s="129"/>
+      <x:c r="C23" s="129"/>
+      <x:c r="D23" s="129"/>
+      <x:c r="E23" s="129"/>
+      <x:c r="F23" s="134"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="138" t="str">
+        <x:v>status.task.loaded</x:v>
+      </x:c>
+      <x:c r="I23" s="138" t="str">
+        <x:v>已载入任务参数。修改后返回“定时任务”保存并启用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="133"/>
+      <x:c r="B24" s="129"/>
+      <x:c r="C24" s="129"/>
+      <x:c r="D24" s="129"/>
+      <x:c r="E24" s="129"/>
+      <x:c r="F24" s="134"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="138" t="str">
+        <x:v>status.task.saved</x:v>
+      </x:c>
+      <x:c r="I24" s="138" t="str">
+        <x:v>任务已保存并启用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="133"/>
+      <x:c r="B25" s="129"/>
+      <x:c r="C25" s="129"/>
+      <x:c r="D25" s="129"/>
+      <x:c r="E25" s="129"/>
+      <x:c r="F25" s="134"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="138" t="str">
         <x:v>error.setup</x:v>
       </x:c>
-      <x:c r="I17" s="128" t="str">
+      <x:c r="I25" s="138" t="str">
         <x:v>初始化失败：</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="2"/>
-      <x:c r="B18" s="2"/>
-      <x:c r="C18" s="2"/>
-      <x:c r="D18" s="2"/>
-      <x:c r="E18" s="2"/>
-      <x:c r="F18" s="2"/>
-      <x:c r="H18" s="128" t="str">
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="133"/>
+      <x:c r="B26" s="129"/>
+      <x:c r="C26" s="129"/>
+      <x:c r="D26" s="129"/>
+      <x:c r="E26" s="129"/>
+      <x:c r="F26" s="134"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="138" t="str">
         <x:v>error.load</x:v>
       </x:c>
-      <x:c r="I18" s="128" t="str">
+      <x:c r="I26" s="138" t="str">
         <x:v>载入模板失败：</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="8" t="str">
-        <x:v>兼容性</x:v>
-      </x:c>
-      <x:c r="B19" s="10"/>
-      <x:c r="C19" s="10"/>
-      <x:c r="D19" s="10"/>
-      <x:c r="E19" s="10"/>
-      <x:c r="F19" s="9"/>
-      <x:c r="H19" s="128" t="str">
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="135"/>
+      <x:c r="B27" s="136"/>
+      <x:c r="C27" s="136"/>
+      <x:c r="D27" s="136"/>
+      <x:c r="E27" s="136"/>
+      <x:c r="F27" s="137"/>
+      <x:c r="G27" s="2"/>
+      <x:c r="H27" s="138" t="str">
         <x:v>error.preview</x:v>
       </x:c>
-      <x:c r="I19" s="128" t="str">
+      <x:c r="I27" s="138" t="str">
         <x:v>预览失败：</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="116" t="str">
-        <x:v>本工具通过 Excel VBA 调用 Outlook 自带的 COM 对象，使用当前 Windows 用户的 Outlook 配置，不需要再次登录。仅支持经典版 Outlook；新版 Outlook 不提供该 COM 接口。工具不包含 PowerShell、第三方 DLL、Java 或自定义 EXE。</x:v>
-      </x:c>
-      <x:c r="B20" s="117"/>
-      <x:c r="C20" s="117"/>
-      <x:c r="D20" s="117"/>
-      <x:c r="E20" s="117"/>
-      <x:c r="F20" s="118"/>
-      <x:c r="H20" s="128" t="str">
-        <x:v>error.action</x:v>
-      </x:c>
-      <x:c r="I20" s="128" t="str">
-        <x:v>操作失败：</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="22" customHeight="1">
-      <x:c r="A21" s="119"/>
-      <x:c r="B21" s="115"/>
-      <x:c r="C21" s="115"/>
-      <x:c r="D21" s="115"/>
-      <x:c r="E21" s="115"/>
-      <x:c r="F21" s="120"/>
-      <x:c r="H21" s="128" t="str">
-        <x:v>error.to</x:v>
-      </x:c>
-      <x:c r="I21" s="128" t="str">
-        <x:v>收件人不能为空。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="119"/>
-      <x:c r="B22" s="115"/>
-      <x:c r="C22" s="115"/>
-      <x:c r="D22" s="115"/>
-      <x:c r="E22" s="115"/>
-      <x:c r="F22" s="120"/>
-      <x:c r="H22" s="128" t="str">
-        <x:v>error.outlook</x:v>
-      </x:c>
-      <x:c r="I22" s="128" t="str">
-        <x:v>无法启动经典版 Outlook。请确认经典版 Outlook 已安装并已登录。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="22" customHeight="1">
-      <x:c r="A23" s="119"/>
-      <x:c r="B23" s="115"/>
-      <x:c r="C23" s="115"/>
-      <x:c r="D23" s="115"/>
-      <x:c r="E23" s="115"/>
-      <x:c r="F23" s="120"/>
-      <x:c r="H23" s="128" t="str">
-        <x:v>error.resolve</x:v>
-      </x:c>
-      <x:c r="I23" s="128" t="str">
-        <x:v>Outlook 无法解析一个或多个收件人/抄送人，请检查地址格式。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="121"/>
-      <x:c r="B24" s="122"/>
-      <x:c r="C24" s="122"/>
-      <x:c r="D24" s="122"/>
-      <x:c r="E24" s="122"/>
-      <x:c r="F24" s="123"/>
-      <x:c r="H24" s="128" t="str">
-        <x:v>error.select</x:v>
-      </x:c>
-      <x:c r="I24" s="128" t="str">
-        <x:v>请选择模板。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="2"/>
-      <x:c r="B25" s="2"/>
-      <x:c r="C25" s="2"/>
-      <x:c r="D25" s="2"/>
-      <x:c r="E25" s="2"/>
-      <x:c r="F25" s="2"/>
-      <x:c r="H25" s="128" t="str">
-        <x:v>error.notfound</x:v>
-      </x:c>
-      <x:c r="I25" s="128" t="str">
-        <x:v>模板库中找不到所选模板。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="2"/>
-      <x:c r="B26" s="2"/>
-      <x:c r="C26" s="2"/>
-      <x:c r="D26" s="2"/>
-      <x:c r="E26" s="2"/>
-      <x:c r="F26" s="2"/>
-      <x:c r="H26" s="128" t="str">
-        <x:v>error.variables</x:v>
-      </x:c>
-      <x:c r="I26" s="128" t="str">
-        <x:v>模板包含的手动变量超过 19 个。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="2"/>
-      <x:c r="B27" s="2"/>
-      <x:c r="C27" s="2"/>
-      <x:c r="D27" s="2"/>
-      <x:c r="E27" s="2"/>
-      <x:c r="F27" s="2"/>
-      <x:c r="H27" s="128" t="str">
-        <x:v>error.unclosed</x:v>
-      </x:c>
-      <x:c r="I27" s="128" t="str">
-        <x:v>模板存在未闭合的变量标记。</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2637,11 +4560,12 @@
       <x:c r="D28" s="2"/>
       <x:c r="E28" s="2"/>
       <x:c r="F28" s="2"/>
-      <x:c r="H28" s="128" t="str">
-        <x:v>error.emptytoken</x:v>
-      </x:c>
-      <x:c r="I28" s="128" t="str">
-        <x:v>模板包含空变量名。</x:v>
+      <x:c r="G28" s="2"/>
+      <x:c r="H28" s="138" t="str">
+        <x:v>error.action</x:v>
+      </x:c>
+      <x:c r="I28" s="138" t="str">
+        <x:v>操作失败：</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2651,11 +4575,12 @@
       <x:c r="D29" s="2"/>
       <x:c r="E29" s="2"/>
       <x:c r="F29" s="2"/>
-      <x:c r="H29" s="128" t="str">
-        <x:v>error.dateformat</x:v>
-      </x:c>
-      <x:c r="I29" s="128" t="str">
-        <x:v>日期变量缺少格式。</x:v>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="138" t="str">
+        <x:v>error.to</x:v>
+      </x:c>
+      <x:c r="I29" s="138" t="str">
+        <x:v>收件人不能为空。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2665,124 +4590,755 @@
       <x:c r="D30" s="2"/>
       <x:c r="E30" s="2"/>
       <x:c r="F30" s="2"/>
-      <x:c r="H30" s="128" t="str">
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="138" t="str">
+        <x:v>error.outlook</x:v>
+      </x:c>
+      <x:c r="I30" s="138" t="str">
+        <x:v>无法启动经典版 Outlook。请确认经典版 Outlook 已安装并已登录。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2"/>
+      <x:c r="B31" s="2"/>
+      <x:c r="C31" s="2"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="138" t="str">
+        <x:v>error.resolve</x:v>
+      </x:c>
+      <x:c r="I31" s="138" t="str">
+        <x:v>Outlook 无法解析一个或多个收件人/抄送人，请检查地址格式。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="138" t="str">
+        <x:v>error.select</x:v>
+      </x:c>
+      <x:c r="I32" s="138" t="str">
+        <x:v>请选择模板。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2"/>
+      <x:c r="B33" s="2"/>
+      <x:c r="C33" s="2"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="138" t="str">
+        <x:v>error.notfound</x:v>
+      </x:c>
+      <x:c r="I33" s="138" t="str">
+        <x:v>模板库中找不到所选模板。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2"/>
+      <x:c r="B34" s="2"/>
+      <x:c r="C34" s="2"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="138" t="str">
+        <x:v>error.variables</x:v>
+      </x:c>
+      <x:c r="I34" s="138" t="str">
+        <x:v>模板包含的参数超过工具支持的数量。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2"/>
+      <x:c r="B35" s="2"/>
+      <x:c r="C35" s="2"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="138" t="str">
+        <x:v>error.unclosed</x:v>
+      </x:c>
+      <x:c r="I35" s="138" t="str">
+        <x:v>模板存在未闭合的变量标记。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2"/>
+      <x:c r="B36" s="2"/>
+      <x:c r="C36" s="2"/>
+      <x:c r="D36" s="2"/>
+      <x:c r="E36" s="2"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="2"/>
+      <x:c r="H36" s="138" t="str">
+        <x:v>error.emptytoken</x:v>
+      </x:c>
+      <x:c r="I36" s="138" t="str">
+        <x:v>模板包含空变量名。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2"/>
+      <x:c r="B37" s="2"/>
+      <x:c r="C37" s="2"/>
+      <x:c r="D37" s="2"/>
+      <x:c r="E37" s="2"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="2"/>
+      <x:c r="H37" s="138" t="str">
+        <x:v>error.dateformat</x:v>
+      </x:c>
+      <x:c r="I37" s="138" t="str">
+        <x:v>日期变量缺少格式。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="2"/>
+      <x:c r="C38" s="2"/>
+      <x:c r="D38" s="2"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
+      <x:c r="H38" s="138" t="str">
         <x:v>error.date</x:v>
       </x:c>
-      <x:c r="I30" s="128" t="str">
+      <x:c r="I38" s="138" t="str">
         <x:v>无法识别日期变量。</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="H31" s="128" t="str">
+    <x:row r="39">
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="2"/>
+      <x:c r="C39" s="2"/>
+      <x:c r="D39" s="2"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
+      <x:c r="H39" s="138" t="str">
         <x:v>error.offset</x:v>
       </x:c>
-      <x:c r="I31" s="128" t="str">
+      <x:c r="I39" s="138" t="str">
         <x:v>日期偏移超出允许范围。</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="H32" s="128" t="str">
+    <x:row r="40">
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+      <x:c r="H40" s="138" t="str">
+        <x:v>error.task.row</x:v>
+      </x:c>
+      <x:c r="I40" s="138" t="str">
+        <x:v>请先在“定时任务”中选择第 6 行以后的任务行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="2"/>
+      <x:c r="B41" s="2"/>
+      <x:c r="C41" s="2"/>
+      <x:c r="D41" s="2"/>
+      <x:c r="E41" s="2"/>
+      <x:c r="F41" s="2"/>
+      <x:c r="G41" s="2"/>
+      <x:c r="H41" s="138" t="str">
+        <x:v>error.task.name</x:v>
+      </x:c>
+      <x:c r="I41" s="138" t="str">
+        <x:v>任务名称不能为空。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="2"/>
+      <x:c r="B42" s="2"/>
+      <x:c r="C42" s="2"/>
+      <x:c r="D42" s="2"/>
+      <x:c r="E42" s="2"/>
+      <x:c r="F42" s="2"/>
+      <x:c r="G42" s="2"/>
+      <x:c r="H42" s="138" t="str">
+        <x:v>error.task.frequency</x:v>
+      </x:c>
+      <x:c r="I42" s="138" t="str">
+        <x:v>频率必须为 1（每天）或 2（每周）。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="2"/>
+      <x:c r="B43" s="2"/>
+      <x:c r="C43" s="2"/>
+      <x:c r="D43" s="2"/>
+      <x:c r="E43" s="2"/>
+      <x:c r="F43" s="2"/>
+      <x:c r="G43" s="2"/>
+      <x:c r="H43" s="138" t="str">
+        <x:v>error.task.weekday</x:v>
+      </x:c>
+      <x:c r="I43" s="138" t="str">
+        <x:v>每周任务的星期必须是 1 至 7（周一至周日）。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="2"/>
+      <x:c r="B44" s="2"/>
+      <x:c r="C44" s="2"/>
+      <x:c r="D44" s="2"/>
+      <x:c r="E44" s="2"/>
+      <x:c r="F44" s="2"/>
+      <x:c r="G44" s="2"/>
+      <x:c r="H44" s="138" t="str">
+        <x:v>error.task.time</x:v>
+      </x:c>
+      <x:c r="I44" s="138" t="str">
+        <x:v>请输入有效发送时间。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="2"/>
+      <x:c r="B45" s="2"/>
+      <x:c r="C45" s="2"/>
+      <x:c r="D45" s="2"/>
+      <x:c r="E45" s="2"/>
+      <x:c r="F45" s="2"/>
+      <x:c r="G45" s="2"/>
+      <x:c r="H45" s="138" t="str">
+        <x:v>error.task.readonly</x:v>
+      </x:c>
+      <x:c r="I45" s="138" t="str">
+        <x:v>工作簿为只读状态，不能安全运行定时发送。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="2"/>
+      <x:c r="B46" s="2"/>
+      <x:c r="C46" s="2"/>
+      <x:c r="D46" s="2"/>
+      <x:c r="E46" s="2"/>
+      <x:c r="F46" s="2"/>
+      <x:c r="G46" s="2"/>
+      <x:c r="H46" s="138" t="str">
         <x:v>confirm.title</x:v>
       </x:c>
-      <x:c r="I32" s="128" t="str">
+      <x:c r="I46" s="138" t="str">
         <x:v>确认直接发送</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
-      <x:c r="H33" s="128" t="str">
+    <x:row r="47">
+      <x:c r="A47" s="2"/>
+      <x:c r="B47" s="2"/>
+      <x:c r="C47" s="2"/>
+      <x:c r="D47" s="2"/>
+      <x:c r="E47" s="2"/>
+      <x:c r="F47" s="2"/>
+      <x:c r="G47" s="2"/>
+      <x:c r="H47" s="138" t="str">
         <x:v>confirm.intro</x:v>
       </x:c>
-      <x:c r="I33" s="128" t="str">
+      <x:c r="I47" s="138" t="str">
         <x:v>邮件将由当前 Outlook 账号直接发送。</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
-      <x:c r="H34" s="128" t="str">
+    <x:row r="48">
+      <x:c r="A48" s="2"/>
+      <x:c r="B48" s="2"/>
+      <x:c r="C48" s="2"/>
+      <x:c r="D48" s="2"/>
+      <x:c r="E48" s="2"/>
+      <x:c r="F48" s="2"/>
+      <x:c r="G48" s="2"/>
+      <x:c r="H48" s="138" t="str">
         <x:v>confirm.to</x:v>
       </x:c>
-      <x:c r="I34" s="128" t="str">
+      <x:c r="I48" s="138" t="str">
         <x:v>收件人：</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
-      <x:c r="H35" s="128" t="str">
+    <x:row r="49">
+      <x:c r="A49" s="2"/>
+      <x:c r="B49" s="2"/>
+      <x:c r="C49" s="2"/>
+      <x:c r="D49" s="2"/>
+      <x:c r="E49" s="2"/>
+      <x:c r="F49" s="2"/>
+      <x:c r="G49" s="2"/>
+      <x:c r="H49" s="138" t="str">
         <x:v>confirm.cc</x:v>
       </x:c>
-      <x:c r="I35" s="128" t="str">
+      <x:c r="I49" s="138" t="str">
         <x:v>抄送：</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
-      <x:c r="H36" s="128" t="str">
+    <x:row r="50">
+      <x:c r="A50" s="2"/>
+      <x:c r="B50" s="2"/>
+      <x:c r="C50" s="2"/>
+      <x:c r="D50" s="2"/>
+      <x:c r="E50" s="2"/>
+      <x:c r="F50" s="2"/>
+      <x:c r="G50" s="2"/>
+      <x:c r="H50" s="138" t="str">
         <x:v>confirm.none</x:v>
       </x:c>
-      <x:c r="I36" s="128" t="str">
+      <x:c r="I50" s="138" t="str">
         <x:v>（无）</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
-      <x:c r="H37" s="128" t="str">
+    <x:row r="51">
+      <x:c r="A51" s="2"/>
+      <x:c r="B51" s="2"/>
+      <x:c r="C51" s="2"/>
+      <x:c r="D51" s="2"/>
+      <x:c r="E51" s="2"/>
+      <x:c r="F51" s="2"/>
+      <x:c r="G51" s="2"/>
+      <x:c r="H51" s="138" t="str">
         <x:v>confirm.subject</x:v>
       </x:c>
-      <x:c r="I37" s="128" t="str">
+      <x:c r="I51" s="138" t="str">
         <x:v>主题：</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
-      <x:c r="H38" s="128" t="str">
+    <x:row r="52">
+      <x:c r="A52" s="2"/>
+      <x:c r="B52" s="2"/>
+      <x:c r="C52" s="2"/>
+      <x:c r="D52" s="2"/>
+      <x:c r="E52" s="2"/>
+      <x:c r="F52" s="2"/>
+      <x:c r="G52" s="2"/>
+      <x:c r="H52" s="138" t="str">
         <x:v>confirm.body</x:v>
       </x:c>
-      <x:c r="I38" s="128" t="str">
+      <x:c r="I52" s="138" t="str">
         <x:v>正文预览：</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
-      <x:c r="H39" s="128" t="str">
+    <x:row r="53">
+      <x:c r="A53" s="2"/>
+      <x:c r="B53" s="2"/>
+      <x:c r="C53" s="2"/>
+      <x:c r="D53" s="2"/>
+      <x:c r="E53" s="2"/>
+      <x:c r="F53" s="2"/>
+      <x:c r="G53" s="2"/>
+      <x:c r="H53" s="138" t="str">
         <x:v>confirm.question</x:v>
       </x:c>
-      <x:c r="I39" s="128" t="str">
+      <x:c r="I53" s="138" t="str">
         <x:v>确认发送吗？</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
-      <x:c r="H40" s="128" t="str">
+    <x:row r="54">
+      <x:c r="A54" s="2"/>
+      <x:c r="B54" s="2"/>
+      <x:c r="C54" s="2"/>
+      <x:c r="D54" s="2"/>
+      <x:c r="E54" s="2"/>
+      <x:c r="F54" s="2"/>
+      <x:c r="G54" s="2"/>
+      <x:c r="H54" s="138" t="str">
+        <x:v>confirm.task.title</x:v>
+      </x:c>
+      <x:c r="I54" s="138" t="str">
+        <x:v>确认启用循环任务</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="2"/>
+      <x:c r="B55" s="2"/>
+      <x:c r="C55" s="2"/>
+      <x:c r="D55" s="2"/>
+      <x:c r="E55" s="2"/>
+      <x:c r="F55" s="2"/>
+      <x:c r="G55" s="2"/>
+      <x:c r="H55" s="138" t="str">
+        <x:v>confirm.task.intro</x:v>
+      </x:c>
+      <x:c r="I55" s="138" t="str">
+        <x:v>确认后，任务到达计划时间时将不再弹窗，直接发送邮件。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="2"/>
+      <x:c r="B56" s="2"/>
+      <x:c r="C56" s="2"/>
+      <x:c r="D56" s="2"/>
+      <x:c r="E56" s="2"/>
+      <x:c r="F56" s="2"/>
+      <x:c r="G56" s="2"/>
+      <x:c r="H56" s="138" t="str">
+        <x:v>confirm.task.frequency.daily</x:v>
+      </x:c>
+      <x:c r="I56" s="138" t="str">
+        <x:v>每天</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="2"/>
+      <x:c r="B57" s="2"/>
+      <x:c r="C57" s="2"/>
+      <x:c r="D57" s="2"/>
+      <x:c r="E57" s="2"/>
+      <x:c r="F57" s="2"/>
+      <x:c r="G57" s="2"/>
+      <x:c r="H57" s="138" t="str">
+        <x:v>confirm.task.frequency.weekly</x:v>
+      </x:c>
+      <x:c r="I57" s="138" t="str">
+        <x:v>每周</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="2"/>
+      <x:c r="B58" s="2"/>
+      <x:c r="C58" s="2"/>
+      <x:c r="D58" s="2"/>
+      <x:c r="E58" s="2"/>
+      <x:c r="F58" s="2"/>
+      <x:c r="G58" s="2"/>
+      <x:c r="H58" s="138" t="str">
+        <x:v>confirm.task.time</x:v>
+      </x:c>
+      <x:c r="I58" s="138" t="str">
+        <x:v>发送时间：</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="2"/>
+      <x:c r="B59" s="2"/>
+      <x:c r="C59" s="2"/>
+      <x:c r="D59" s="2"/>
+      <x:c r="E59" s="2"/>
+      <x:c r="F59" s="2"/>
+      <x:c r="G59" s="2"/>
+      <x:c r="H59" s="138" t="str">
+        <x:v>confirm.task.template</x:v>
+      </x:c>
+      <x:c r="I59" s="138" t="str">
+        <x:v>模板：</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="2"/>
+      <x:c r="B60" s="2"/>
+      <x:c r="C60" s="2"/>
+      <x:c r="D60" s="2"/>
+      <x:c r="E60" s="2"/>
+      <x:c r="F60" s="2"/>
+      <x:c r="G60" s="2"/>
+      <x:c r="H60" s="138" t="str">
+        <x:v>confirm.task.name</x:v>
+      </x:c>
+      <x:c r="I60" s="138" t="str">
+        <x:v>任务：</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="2"/>
+      <x:c r="B61" s="2"/>
+      <x:c r="C61" s="2"/>
+      <x:c r="D61" s="2"/>
+      <x:c r="E61" s="2"/>
+      <x:c r="F61" s="2"/>
+      <x:c r="G61" s="2"/>
+      <x:c r="H61" s="138" t="str">
+        <x:v>task.status.ready</x:v>
+      </x:c>
+      <x:c r="I61" s="138" t="str">
+        <x:v>等待发送</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="2"/>
+      <x:c r="B62" s="2"/>
+      <x:c r="C62" s="2"/>
+      <x:c r="D62" s="2"/>
+      <x:c r="E62" s="2"/>
+      <x:c r="F62" s="2"/>
+      <x:c r="G62" s="2"/>
+      <x:c r="H62" s="138" t="str">
+        <x:v>task.status.sending</x:v>
+      </x:c>
+      <x:c r="I62" s="138" t="str">
+        <x:v>正在发送</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="2"/>
+      <x:c r="B63" s="2"/>
+      <x:c r="C63" s="2"/>
+      <x:c r="D63" s="2"/>
+      <x:c r="E63" s="2"/>
+      <x:c r="F63" s="2"/>
+      <x:c r="G63" s="2"/>
+      <x:c r="H63" s="138" t="str">
+        <x:v>task.status.sent</x:v>
+      </x:c>
+      <x:c r="I63" s="138" t="str">
+        <x:v>已发送</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="2"/>
+      <x:c r="B64" s="2"/>
+      <x:c r="C64" s="2"/>
+      <x:c r="D64" s="2"/>
+      <x:c r="E64" s="2"/>
+      <x:c r="F64" s="2"/>
+      <x:c r="G64" s="2"/>
+      <x:c r="H64" s="138" t="str">
+        <x:v>task.status.missed</x:v>
+      </x:c>
+      <x:c r="I64" s="138" t="str">
+        <x:v>已错过</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="2"/>
+      <x:c r="B65" s="2"/>
+      <x:c r="C65" s="2"/>
+      <x:c r="D65" s="2"/>
+      <x:c r="E65" s="2"/>
+      <x:c r="F65" s="2"/>
+      <x:c r="G65" s="2"/>
+      <x:c r="H65" s="138" t="str">
+        <x:v>task.status.failed</x:v>
+      </x:c>
+      <x:c r="I65" s="138" t="str">
+        <x:v>发送失败</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="2"/>
+      <x:c r="B66" s="2"/>
+      <x:c r="C66" s="2"/>
+      <x:c r="D66" s="2"/>
+      <x:c r="E66" s="2"/>
+      <x:c r="F66" s="2"/>
+      <x:c r="G66" s="2"/>
+      <x:c r="H66" s="138" t="str">
+        <x:v>task.status.uncertain</x:v>
+      </x:c>
+      <x:c r="I66" s="138" t="str">
+        <x:v>结果不确定</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="2"/>
+      <x:c r="B67" s="2"/>
+      <x:c r="C67" s="2"/>
+      <x:c r="D67" s="2"/>
+      <x:c r="E67" s="2"/>
+      <x:c r="F67" s="2"/>
+      <x:c r="G67" s="2"/>
+      <x:c r="H67" s="138" t="str">
+        <x:v>task.status.paused</x:v>
+      </x:c>
+      <x:c r="I67" s="138" t="str">
+        <x:v>已暂停</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="2"/>
+      <x:c r="B68" s="2"/>
+      <x:c r="C68" s="2"/>
+      <x:c r="D68" s="2"/>
+      <x:c r="E68" s="2"/>
+      <x:c r="F68" s="2"/>
+      <x:c r="G68" s="2"/>
+      <x:c r="H68" s="138" t="str">
+        <x:v>task.status.changed</x:v>
+      </x:c>
+      <x:c r="I68" s="138" t="str">
+        <x:v>模板已变化，等待重新确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="2"/>
+      <x:c r="B69" s="2"/>
+      <x:c r="C69" s="2"/>
+      <x:c r="D69" s="2"/>
+      <x:c r="E69" s="2"/>
+      <x:c r="F69" s="2"/>
+      <x:c r="G69" s="2"/>
+      <x:c r="H69" s="138" t="str">
+        <x:v>task.detail.missed</x:v>
+      </x:c>
+      <x:c r="I69" s="138" t="str">
+        <x:v>计划时间已经过去，本次不补发。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="2"/>
+      <x:c r="B70" s="2"/>
+      <x:c r="C70" s="2"/>
+      <x:c r="D70" s="2"/>
+      <x:c r="E70" s="2"/>
+      <x:c r="F70" s="2"/>
+      <x:c r="G70" s="2"/>
+      <x:c r="H70" s="138" t="str">
+        <x:v>task.detail.sent</x:v>
+      </x:c>
+      <x:c r="I70" s="138" t="str">
+        <x:v>邮件已交给 Outlook 发送。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="2"/>
+      <x:c r="B71" s="2"/>
+      <x:c r="C71" s="2"/>
+      <x:c r="D71" s="2"/>
+      <x:c r="E71" s="2"/>
+      <x:c r="F71" s="2"/>
+      <x:c r="G71" s="2"/>
+      <x:c r="H71" s="138" t="str">
+        <x:v>task.detail.duplicate</x:v>
+      </x:c>
+      <x:c r="I71" s="138" t="str">
+        <x:v>本计划周期已有记录，未重复发送。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="2"/>
+      <x:c r="B72" s="2"/>
+      <x:c r="C72" s="2"/>
+      <x:c r="D72" s="2"/>
+      <x:c r="E72" s="2"/>
+      <x:c r="F72" s="2"/>
+      <x:c r="G72" s="2"/>
+      <x:c r="H72" s="138" t="str">
+        <x:v>scroll.position</x:v>
+      </x:c>
+      <x:c r="I72" s="138" t="str">
+        <x:v>参数位置</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="2"/>
+      <x:c r="B73" s="2"/>
+      <x:c r="C73" s="2"/>
+      <x:c r="D73" s="2"/>
+      <x:c r="E73" s="2"/>
+      <x:c r="F73" s="2"/>
+      <x:c r="G73" s="2"/>
+      <x:c r="H73" s="138" t="str">
         <x:v>ellipsis</x:v>
       </x:c>
-      <x:c r="I40" s="128" t="str">
+      <x:c r="I73" s="138" t="str">
         <x:v>……</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
-      <x:c r="H41" s="128" t="str">
+    <x:row r="74">
+      <x:c r="A74" s="2"/>
+      <x:c r="B74" s="2"/>
+      <x:c r="C74" s="2"/>
+      <x:c r="D74" s="2"/>
+      <x:c r="E74" s="2"/>
+      <x:c r="F74" s="2"/>
+      <x:c r="G74" s="2"/>
+      <x:c r="H74" s="138" t="str">
         <x:v>app.title</x:v>
       </x:c>
-      <x:c r="I41" s="128" t="str">
+      <x:c r="I74" s="138" t="str">
         <x:v>Outlook 邮件模板工具</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
-      <x:c r="H42" s="128" t="str">
+    <x:row r="75">
+      <x:c r="A75" s="2"/>
+      <x:c r="B75" s="2"/>
+      <x:c r="C75" s="2"/>
+      <x:c r="D75" s="2"/>
+      <x:c r="E75" s="2"/>
+      <x:c r="F75" s="2"/>
+      <x:c r="G75" s="2"/>
+      <x:c r="H75" s="138" t="str">
         <x:v>token.today</x:v>
       </x:c>
-      <x:c r="I42" s="128" t="str">
+      <x:c r="I75" s="138" t="str">
         <x:v>今天</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
-      <x:c r="H43" s="128" t="str">
+    <x:row r="76">
+      <x:c r="A76" s="2"/>
+      <x:c r="B76" s="2"/>
+      <x:c r="C76" s="2"/>
+      <x:c r="D76" s="2"/>
+      <x:c r="E76" s="2"/>
+      <x:c r="F76" s="2"/>
+      <x:c r="G76" s="2"/>
+      <x:c r="H76" s="138" t="str">
         <x:v>token.day</x:v>
       </x:c>
-      <x:c r="I43" s="128" t="str">
+      <x:c r="I76" s="138" t="str">
         <x:v>天</x:v>
       </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="2"/>
+      <x:c r="B77" s="2"/>
+      <x:c r="C77" s="2"/>
+      <x:c r="D77" s="2"/>
+      <x:c r="E77" s="2"/>
+      <x:c r="F77" s="2"/>
+      <x:c r="G77" s="2"/>
+      <x:c r="H77" s="2"/>
+      <x:c r="I77" s="2"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="2"/>
+      <x:c r="B78" s="2"/>
+      <x:c r="C78" s="2"/>
+      <x:c r="D78" s="2"/>
+      <x:c r="E78" s="2"/>
+      <x:c r="F78" s="2"/>
+      <x:c r="G78" s="2"/>
+      <x:c r="H78" s="2"/>
+      <x:c r="I78" s="2"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="2"/>
+      <x:c r="B79" s="2"/>
+      <x:c r="C79" s="2"/>
+      <x:c r="D79" s="2"/>
+      <x:c r="E79" s="2"/>
+      <x:c r="F79" s="2"/>
+      <x:c r="G79" s="2"/>
+      <x:c r="H79" s="2"/>
+      <x:c r="I79" s="2"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="2"/>
+      <x:c r="B80" s="2"/>
+      <x:c r="C80" s="2"/>
+      <x:c r="D80" s="2"/>
+      <x:c r="E80" s="2"/>
+      <x:c r="F80" s="2"/>
+      <x:c r="G80" s="2"/>
+      <x:c r="H80" s="2"/>
+      <x:c r="I80" s="2"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A4:B4"/>
-    <x:mergeCell ref="A11:F11"/>
-    <x:mergeCell ref="A12:F17"/>
-    <x:mergeCell ref="A19:F19"/>
-    <x:mergeCell ref="A20:F24"/>
+    <x:mergeCell ref="A12:F12"/>
+    <x:mergeCell ref="A13:F18"/>
+    <x:mergeCell ref="A20:F20"/>
+    <x:mergeCell ref="A21:F27"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
